--- a/Gantt-chart TIMELINE per 3 Maret 2026 rev_1.xlsx
+++ b/Gantt-chart TIMELINE per 3 Maret 2026 rev_1.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7620"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19635" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="GanttChart" sheetId="9" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="vertex42_id" hidden="1">"gantt-chart_L.xlsx"</definedName>
     <definedName name="vertex42_title" hidden="1">"Gantt Chart Template"</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -852,7 +852,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="241">
   <si>
     <t>RICEF BY LEUWITEX ( update 3 Maret 2026 )</t>
   </si>
@@ -992,24 +992,15 @@
     <t>DETAIL LIST KARTON PER RAK</t>
   </si>
   <si>
-    <t>Budi/Star</t>
-  </si>
-  <si>
     <t>LAPORAN GUDANG PACKING LEAD TIME</t>
   </si>
   <si>
-    <t>Baim/Star</t>
-  </si>
-  <si>
     <t>MOVING HISTORY PER LIST KARTON</t>
   </si>
   <si>
     <t>DASHBOARD LAYOUT PER BIN</t>
   </si>
   <si>
-    <t>Baim/Jali</t>
-  </si>
-  <si>
     <t>LAPORAN SURAT JALAN SLOC</t>
   </si>
   <si>
@@ -1050,9 +1041,6 @@
   </si>
   <si>
     <t>REPORT RESERVASI</t>
-  </si>
-  <si>
-    <t>Budi/Jali</t>
   </si>
   <si>
     <t>REPORT RESUME KODE PARTAI</t>
@@ -2347,19 +2335,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="9">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="ddd\ m/dd/yy"/>
-    <numFmt numFmtId="179" formatCode="m/d/yyyy\ \(dddd\)"/>
-    <numFmt numFmtId="180" formatCode="d\ mmm\ yyyy"/>
-    <numFmt numFmtId="181" formatCode="d"/>
-    <numFmt numFmtId="182" formatCode="ddd\ dd/m/yy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="5">
+    <numFmt numFmtId="166" formatCode="ddd\ m/dd/yy"/>
+    <numFmt numFmtId="167" formatCode="m/d/yyyy\ \(dddd\)"/>
+    <numFmt numFmtId="168" formatCode="d\ mmm\ yyyy"/>
+    <numFmt numFmtId="169" formatCode="d"/>
+    <numFmt numFmtId="170" formatCode="ddd\ dd/m/yy"/>
   </numFmts>
-  <fonts count="70">
+  <fonts count="51">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2533,7 +2517,7 @@
     <font>
       <i/>
       <sz val="8"/>
-      <color theme="0" tint="-0.349986266670736"/>
+      <color theme="0" tint="-0.34998626667073579"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -2609,149 +2593,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <name val="Arial"/>
@@ -2776,11 +2617,6 @@
       <i/>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="SimSun"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2816,8 +2652,13 @@
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="45">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2826,13 +2667,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.799737540818506"/>
+        <fgColor theme="3" tint="0.79970702230903046"/>
         <bgColor rgb="FFD6F4D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.799737540818506"/>
+        <fgColor theme="3" tint="0.79970702230903046"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2844,7 +2685,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149754325998718"/>
+        <fgColor theme="0" tint="-0.14972380748924222"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2856,13 +2697,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799829096346934"/>
+        <fgColor theme="6" tint="0.79979857783745845"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79985961485641"/>
+        <fgColor theme="6" tint="0.79982909634693444"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2880,7 +2721,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.799981688894314"/>
+        <fgColor theme="3" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2898,192 +2739,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="0"/>
+        <bgColor rgb="FFD6F4D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -3157,16 +2818,16 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top/>
       <bottom/>
@@ -3174,10 +2835,10 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top/>
       <bottom/>
@@ -3185,10 +2846,10 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right style="medium">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top/>
       <bottom/>
@@ -3198,10 +2859,10 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3210,46 +2871,46 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right style="medium">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3262,252 +2923,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="9" fontId="50" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="14" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="16" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="16" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="17" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3524,16 +2949,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3541,9 +2966,6 @@
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3556,7 +2978,7 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3565,7 +2987,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3577,7 +2999,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3588,9 +3010,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3610,7 +3029,7 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3642,16 +3061,13 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3668,9 +3084,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -3678,7 +3091,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
@@ -3686,50 +3099,24 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="6" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="2" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="34" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="34" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="180" fontId="34" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="34" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="34" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3765,16 +3152,16 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="1" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="1" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="5" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="1" fillId="5" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="5" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="1" fillId="5" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3807,7 +3194,7 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3828,13 +3215,13 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="1" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3846,65 +3233,128 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="34" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="34" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="34" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="11">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <border>
         <left style="thin">
@@ -3926,18 +3376,14 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4009,10 +3455,10 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
-      <color rgb="00FFCCCC"/>
-      <color rgb="00FF9900"/>
-      <color rgb="0091D0FF"/>
-      <color rgb="00CC00CC"/>
+      <color rgb="FFFFCCCC"/>
+      <color rgb="FFFF9900"/>
+      <color rgb="FF91D0FF"/>
+      <color rgb="FFCC00CC"/>
     </mruColors>
   </colors>
   <extLst>
@@ -4024,11 +3470,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="22" fmlaLink="$H$4" horiz="1" max="100" min="1" val="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="22" fmlaLink="$H$4" horiz="1" max="100" min="1" page="0"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -4042,7 +3488,7 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>80433</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="8236" name="Text Box 44" hidden="1"/>
         <xdr:cNvSpPr txBox="1">
@@ -4090,7 +3536,7 @@
           <xdr:row>2</xdr:row>
           <xdr:rowOff>114300</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8238" name="Scroll Bar 46" hidden="1">
               <a:extLst>
@@ -4103,8 +3549,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9248775" y="504825"/>
-              <a:ext cx="2886075" cy="219075"/>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4120,7 +3566,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -4142,7 +3588,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -4171,14 +3617,14 @@
           <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
             <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
               <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
               </a:solidFill>
             </a14:hiddenFill>
           </a:ext>
           <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
             <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="1">
               <a:solidFill>
-                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
               </a:solidFill>
               <a:miter lim="800000"/>
               <a:headEnd/>
@@ -4220,7 +3666,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -4247,7 +3693,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -4269,7 +3715,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -4296,7 +3742,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -4318,7 +3764,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -4345,7 +3791,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -4359,7 +3805,7 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="12289" name="AutoShape 1" descr="blob:https://web.whatsapp.com/4841a61e-759f-484d-9013-f081556103c8"/>
         <xdr:cNvSpPr>
@@ -4401,7 +3847,7 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="12291" name="AutoShape 3" descr="blob:https://web.whatsapp.com/4841a61e-759f-484d-9013-f081556103c8"/>
         <xdr:cNvSpPr>
@@ -4714,861 +4160,862 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BN115"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.85714285714286" customWidth="1"/>
-    <col min="2" max="2" width="59.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="13.4285714285714" customWidth="1"/>
+    <col min="1" max="1" width="6.85546875" customWidth="1"/>
+    <col min="2" max="2" width="59.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="6.71428571428571" customWidth="1"/>
-    <col min="9" max="9" width="6.42857142857143" customWidth="1"/>
-    <col min="10" max="10" width="1.85714285714286" customWidth="1"/>
-    <col min="11" max="66" width="2.42857142857143" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" customWidth="1"/>
+    <col min="9" max="9" width="6.42578125" customWidth="1"/>
+    <col min="10" max="10" width="1.85546875" customWidth="1"/>
+    <col min="11" max="66" width="2.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:66">
-      <c r="A1" s="59" t="s">
+    <row r="1" spans="1:66" ht="30" customHeight="1">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="I1" s="61"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="62"/>
-      <c r="AB1" s="62"/>
-      <c r="AC1" s="62"/>
-      <c r="AD1" s="62"/>
-      <c r="AE1" s="62"/>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:66">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="H2" s="67"/>
-    </row>
-    <row r="3" ht="14.25" spans="1:66">
-      <c r="A3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
-      <c r="V3" s="68"/>
-      <c r="W3" s="68"/>
-      <c r="X3" s="68"/>
-      <c r="Y3" s="68"/>
-      <c r="Z3" s="68"/>
-      <c r="AA3" s="68"/>
-    </row>
-    <row r="4" ht="17.25" customHeight="1" spans="1:66">
-      <c r="A4" s="69"/>
-      <c r="B4" s="70" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="I1" s="58"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
+      <c r="V1" s="111"/>
+      <c r="W1" s="111"/>
+      <c r="X1" s="111"/>
+      <c r="Y1" s="111"/>
+      <c r="Z1" s="111"/>
+      <c r="AA1" s="111"/>
+      <c r="AB1" s="111"/>
+      <c r="AC1" s="111"/>
+      <c r="AD1" s="111"/>
+      <c r="AE1" s="111"/>
+    </row>
+    <row r="2" spans="1:66" ht="18" customHeight="1">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="H2" s="63"/>
+    </row>
+    <row r="3" spans="1:66" ht="14.25">
+      <c r="A3" s="59"/>
+      <c r="H3" s="63"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="64"/>
+      <c r="W3" s="64"/>
+      <c r="X3" s="64"/>
+      <c r="Y3" s="64"/>
+      <c r="Z3" s="64"/>
+      <c r="AA3" s="64"/>
+    </row>
+    <row r="4" spans="1:66" ht="17.25" customHeight="1">
+      <c r="A4" s="65"/>
+      <c r="B4" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="71">
+      <c r="C4" s="112">
         <v>45986</v>
       </c>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="70" t="s">
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="72">
+      <c r="H4" s="67">
         <v>1</v>
       </c>
-      <c r="J4" s="69"/>
-      <c r="K4" s="73" t="str">
+      <c r="J4" s="65"/>
+      <c r="K4" s="113" t="str">
         <f>"Week "&amp;(K6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 1</v>
       </c>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="73" t="str">
+      <c r="L4" s="114"/>
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="114"/>
+      <c r="P4" s="114"/>
+      <c r="Q4" s="115"/>
+      <c r="R4" s="113" t="str">
         <f>"Week "&amp;(R6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 2</v>
       </c>
-      <c r="S4" s="74"/>
-      <c r="T4" s="74"/>
-      <c r="U4" s="74"/>
-      <c r="V4" s="74"/>
-      <c r="W4" s="74"/>
-      <c r="X4" s="75"/>
-      <c r="Y4" s="73" t="str">
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114"/>
+      <c r="V4" s="114"/>
+      <c r="W4" s="114"/>
+      <c r="X4" s="115"/>
+      <c r="Y4" s="113" t="str">
         <f>"Week "&amp;(Y6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 3</v>
       </c>
-      <c r="Z4" s="74"/>
-      <c r="AA4" s="74"/>
-      <c r="AB4" s="74"/>
-      <c r="AC4" s="74"/>
-      <c r="AD4" s="74"/>
-      <c r="AE4" s="75"/>
-      <c r="AF4" s="73" t="str">
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="114"/>
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="113" t="str">
         <f>"Week "&amp;(AF6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 4</v>
       </c>
-      <c r="AG4" s="74"/>
-      <c r="AH4" s="74"/>
-      <c r="AI4" s="74"/>
-      <c r="AJ4" s="74"/>
-      <c r="AK4" s="74"/>
-      <c r="AL4" s="75"/>
-      <c r="AM4" s="73" t="str">
+      <c r="AG4" s="114"/>
+      <c r="AH4" s="114"/>
+      <c r="AI4" s="114"/>
+      <c r="AJ4" s="114"/>
+      <c r="AK4" s="114"/>
+      <c r="AL4" s="115"/>
+      <c r="AM4" s="113" t="str">
         <f>"Week "&amp;(AM6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AN4" s="74"/>
-      <c r="AO4" s="74"/>
-      <c r="AP4" s="74"/>
-      <c r="AQ4" s="74"/>
-      <c r="AR4" s="74"/>
-      <c r="AS4" s="75"/>
-      <c r="AT4" s="73" t="str">
+      <c r="AN4" s="114"/>
+      <c r="AO4" s="114"/>
+      <c r="AP4" s="114"/>
+      <c r="AQ4" s="114"/>
+      <c r="AR4" s="114"/>
+      <c r="AS4" s="115"/>
+      <c r="AT4" s="113" t="str">
         <f>"Week "&amp;(AT6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AU4" s="74"/>
-      <c r="AV4" s="74"/>
-      <c r="AW4" s="74"/>
-      <c r="AX4" s="74"/>
-      <c r="AY4" s="74"/>
-      <c r="AZ4" s="75"/>
-      <c r="BA4" s="73" t="str">
+      <c r="AU4" s="114"/>
+      <c r="AV4" s="114"/>
+      <c r="AW4" s="114"/>
+      <c r="AX4" s="114"/>
+      <c r="AY4" s="114"/>
+      <c r="AZ4" s="115"/>
+      <c r="BA4" s="113" t="str">
         <f>"Week "&amp;(BA6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 7</v>
       </c>
-      <c r="BB4" s="74"/>
-      <c r="BC4" s="74"/>
-      <c r="BD4" s="74"/>
-      <c r="BE4" s="74"/>
-      <c r="BF4" s="74"/>
-      <c r="BG4" s="75"/>
-      <c r="BH4" s="73" t="str">
+      <c r="BB4" s="114"/>
+      <c r="BC4" s="114"/>
+      <c r="BD4" s="114"/>
+      <c r="BE4" s="114"/>
+      <c r="BF4" s="114"/>
+      <c r="BG4" s="115"/>
+      <c r="BH4" s="113" t="str">
         <f>"Week "&amp;(BH6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BI4" s="74"/>
-      <c r="BJ4" s="74"/>
-      <c r="BK4" s="74"/>
-      <c r="BL4" s="74"/>
-      <c r="BM4" s="74"/>
-      <c r="BN4" s="75"/>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" spans="1:66">
-      <c r="A5" s="69"/>
-      <c r="B5" s="70" t="s">
+      <c r="BI4" s="114"/>
+      <c r="BJ4" s="114"/>
+      <c r="BK4" s="114"/>
+      <c r="BL4" s="114"/>
+      <c r="BM4" s="114"/>
+      <c r="BN4" s="115"/>
+    </row>
+    <row r="5" spans="1:66" ht="17.25" customHeight="1">
+      <c r="A5" s="65"/>
+      <c r="B5" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="77">
+      <c r="D5" s="116"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="117">
         <f>K6</f>
         <v>45985</v>
       </c>
-      <c r="L5" s="78"/>
-      <c r="M5" s="78"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="79"/>
-      <c r="R5" s="77">
+      <c r="L5" s="118"/>
+      <c r="M5" s="118"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="118"/>
+      <c r="P5" s="118"/>
+      <c r="Q5" s="119"/>
+      <c r="R5" s="117">
         <f>R6</f>
         <v>45992</v>
       </c>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
-      <c r="U5" s="78"/>
-      <c r="V5" s="78"/>
-      <c r="W5" s="78"/>
-      <c r="X5" s="79"/>
-      <c r="Y5" s="77">
+      <c r="S5" s="118"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="118"/>
+      <c r="V5" s="118"/>
+      <c r="W5" s="118"/>
+      <c r="X5" s="119"/>
+      <c r="Y5" s="117">
         <f>Y6</f>
         <v>45999</v>
       </c>
-      <c r="Z5" s="78"/>
-      <c r="AA5" s="78"/>
-      <c r="AB5" s="78"/>
-      <c r="AC5" s="78"/>
-      <c r="AD5" s="78"/>
-      <c r="AE5" s="79"/>
-      <c r="AF5" s="77">
+      <c r="Z5" s="118"/>
+      <c r="AA5" s="118"/>
+      <c r="AB5" s="118"/>
+      <c r="AC5" s="118"/>
+      <c r="AD5" s="118"/>
+      <c r="AE5" s="119"/>
+      <c r="AF5" s="117">
         <f>AF6</f>
         <v>46006</v>
       </c>
-      <c r="AG5" s="78"/>
-      <c r="AH5" s="78"/>
-      <c r="AI5" s="78"/>
-      <c r="AJ5" s="78"/>
-      <c r="AK5" s="78"/>
-      <c r="AL5" s="79"/>
-      <c r="AM5" s="77">
+      <c r="AG5" s="118"/>
+      <c r="AH5" s="118"/>
+      <c r="AI5" s="118"/>
+      <c r="AJ5" s="118"/>
+      <c r="AK5" s="118"/>
+      <c r="AL5" s="119"/>
+      <c r="AM5" s="117">
         <f>AM6</f>
         <v>46013</v>
       </c>
-      <c r="AN5" s="78"/>
-      <c r="AO5" s="78"/>
-      <c r="AP5" s="78"/>
-      <c r="AQ5" s="78"/>
-      <c r="AR5" s="78"/>
-      <c r="AS5" s="79"/>
-      <c r="AT5" s="77">
+      <c r="AN5" s="118"/>
+      <c r="AO5" s="118"/>
+      <c r="AP5" s="118"/>
+      <c r="AQ5" s="118"/>
+      <c r="AR5" s="118"/>
+      <c r="AS5" s="119"/>
+      <c r="AT5" s="117">
         <f>AT6</f>
         <v>46020</v>
       </c>
-      <c r="AU5" s="78"/>
-      <c r="AV5" s="78"/>
-      <c r="AW5" s="78"/>
-      <c r="AX5" s="78"/>
-      <c r="AY5" s="78"/>
-      <c r="AZ5" s="79"/>
-      <c r="BA5" s="77">
+      <c r="AU5" s="118"/>
+      <c r="AV5" s="118"/>
+      <c r="AW5" s="118"/>
+      <c r="AX5" s="118"/>
+      <c r="AY5" s="118"/>
+      <c r="AZ5" s="119"/>
+      <c r="BA5" s="117">
         <f>BA6</f>
         <v>46027</v>
       </c>
-      <c r="BB5" s="78"/>
-      <c r="BC5" s="78"/>
-      <c r="BD5" s="78"/>
-      <c r="BE5" s="78"/>
-      <c r="BF5" s="78"/>
-      <c r="BG5" s="79"/>
-      <c r="BH5" s="77">
+      <c r="BB5" s="118"/>
+      <c r="BC5" s="118"/>
+      <c r="BD5" s="118"/>
+      <c r="BE5" s="118"/>
+      <c r="BF5" s="118"/>
+      <c r="BG5" s="119"/>
+      <c r="BH5" s="117">
         <f>BH6</f>
         <v>46034</v>
       </c>
-      <c r="BI5" s="78"/>
-      <c r="BJ5" s="78"/>
-      <c r="BK5" s="78"/>
-      <c r="BL5" s="78"/>
-      <c r="BM5" s="78"/>
-      <c r="BN5" s="79"/>
+      <c r="BI5" s="118"/>
+      <c r="BJ5" s="118"/>
+      <c r="BK5" s="118"/>
+      <c r="BL5" s="118"/>
+      <c r="BM5" s="118"/>
+      <c r="BN5" s="119"/>
     </row>
     <row r="6" spans="1:66">
-      <c r="A6" s="69"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="80">
+      <c r="A6" s="65"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="68">
         <f>C4-WEEKDAY(C4,1)+2+7*(H4-1)</f>
         <v>45985</v>
       </c>
-      <c r="L6" s="81">
+      <c r="L6" s="69">
         <f t="shared" ref="L6:AQ6" si="0">K6+1</f>
         <v>45986</v>
       </c>
-      <c r="M6" s="81">
+      <c r="M6" s="69">
         <f t="shared" si="0"/>
         <v>45987</v>
       </c>
-      <c r="N6" s="81">
+      <c r="N6" s="69">
         <f t="shared" si="0"/>
         <v>45988</v>
       </c>
-      <c r="O6" s="81">
+      <c r="O6" s="69">
         <f t="shared" si="0"/>
         <v>45989</v>
       </c>
-      <c r="P6" s="81">
+      <c r="P6" s="69">
         <f t="shared" si="0"/>
         <v>45990</v>
       </c>
-      <c r="Q6" s="82">
+      <c r="Q6" s="70">
         <f t="shared" si="0"/>
         <v>45991</v>
       </c>
-      <c r="R6" s="80">
+      <c r="R6" s="68">
         <f t="shared" si="0"/>
         <v>45992</v>
       </c>
-      <c r="S6" s="81">
+      <c r="S6" s="69">
         <f t="shared" si="0"/>
         <v>45993</v>
       </c>
-      <c r="T6" s="81">
+      <c r="T6" s="69">
         <f t="shared" si="0"/>
         <v>45994</v>
       </c>
-      <c r="U6" s="81">
+      <c r="U6" s="69">
         <f t="shared" si="0"/>
         <v>45995</v>
       </c>
-      <c r="V6" s="81">
+      <c r="V6" s="69">
         <f t="shared" si="0"/>
         <v>45996</v>
       </c>
-      <c r="W6" s="81">
+      <c r="W6" s="69">
         <f t="shared" si="0"/>
         <v>45997</v>
       </c>
-      <c r="X6" s="82">
+      <c r="X6" s="70">
         <f t="shared" si="0"/>
         <v>45998</v>
       </c>
-      <c r="Y6" s="80">
+      <c r="Y6" s="68">
         <f t="shared" si="0"/>
         <v>45999</v>
       </c>
-      <c r="Z6" s="81">
+      <c r="Z6" s="69">
         <f t="shared" si="0"/>
         <v>46000</v>
       </c>
-      <c r="AA6" s="81">
+      <c r="AA6" s="69">
         <f t="shared" si="0"/>
         <v>46001</v>
       </c>
-      <c r="AB6" s="81">
+      <c r="AB6" s="69">
         <f t="shared" si="0"/>
         <v>46002</v>
       </c>
-      <c r="AC6" s="81">
+      <c r="AC6" s="69">
         <f t="shared" si="0"/>
         <v>46003</v>
       </c>
-      <c r="AD6" s="81">
+      <c r="AD6" s="69">
         <f t="shared" si="0"/>
         <v>46004</v>
       </c>
-      <c r="AE6" s="82">
+      <c r="AE6" s="70">
         <f t="shared" si="0"/>
         <v>46005</v>
       </c>
-      <c r="AF6" s="80">
+      <c r="AF6" s="68">
         <f t="shared" si="0"/>
         <v>46006</v>
       </c>
-      <c r="AG6" s="81">
+      <c r="AG6" s="69">
         <f t="shared" si="0"/>
         <v>46007</v>
       </c>
-      <c r="AH6" s="81">
+      <c r="AH6" s="69">
         <f t="shared" si="0"/>
         <v>46008</v>
       </c>
-      <c r="AI6" s="81">
+      <c r="AI6" s="69">
         <f t="shared" si="0"/>
         <v>46009</v>
       </c>
-      <c r="AJ6" s="81">
+      <c r="AJ6" s="69">
         <f t="shared" si="0"/>
         <v>46010</v>
       </c>
-      <c r="AK6" s="81">
+      <c r="AK6" s="69">
         <f t="shared" si="0"/>
         <v>46011</v>
       </c>
-      <c r="AL6" s="82">
+      <c r="AL6" s="70">
         <f t="shared" si="0"/>
         <v>46012</v>
       </c>
-      <c r="AM6" s="80">
+      <c r="AM6" s="68">
         <f t="shared" si="0"/>
         <v>46013</v>
       </c>
-      <c r="AN6" s="81">
+      <c r="AN6" s="69">
         <f t="shared" si="0"/>
         <v>46014</v>
       </c>
-      <c r="AO6" s="81">
+      <c r="AO6" s="69">
         <f t="shared" si="0"/>
         <v>46015</v>
       </c>
-      <c r="AP6" s="81">
+      <c r="AP6" s="69">
         <f t="shared" si="0"/>
         <v>46016</v>
       </c>
-      <c r="AQ6" s="81">
+      <c r="AQ6" s="69">
         <f t="shared" si="0"/>
         <v>46017</v>
       </c>
-      <c r="AR6" s="81">
+      <c r="AR6" s="69">
         <f t="shared" ref="AR6:BN6" si="1">AQ6+1</f>
         <v>46018</v>
       </c>
-      <c r="AS6" s="82">
+      <c r="AS6" s="70">
         <f t="shared" si="1"/>
         <v>46019</v>
       </c>
-      <c r="AT6" s="80">
+      <c r="AT6" s="68">
         <f t="shared" si="1"/>
         <v>46020</v>
       </c>
-      <c r="AU6" s="81">
+      <c r="AU6" s="69">
         <f t="shared" si="1"/>
         <v>46021</v>
       </c>
-      <c r="AV6" s="81">
+      <c r="AV6" s="69">
         <f t="shared" si="1"/>
         <v>46022</v>
       </c>
-      <c r="AW6" s="81">
+      <c r="AW6" s="69">
         <f t="shared" si="1"/>
         <v>46023</v>
       </c>
-      <c r="AX6" s="81">
+      <c r="AX6" s="69">
         <f t="shared" si="1"/>
         <v>46024</v>
       </c>
-      <c r="AY6" s="81">
+      <c r="AY6" s="69">
         <f t="shared" si="1"/>
         <v>46025</v>
       </c>
-      <c r="AZ6" s="82">
+      <c r="AZ6" s="70">
         <f t="shared" si="1"/>
         <v>46026</v>
       </c>
-      <c r="BA6" s="80">
+      <c r="BA6" s="68">
         <f t="shared" si="1"/>
         <v>46027</v>
       </c>
-      <c r="BB6" s="81">
+      <c r="BB6" s="69">
         <f t="shared" si="1"/>
         <v>46028</v>
       </c>
-      <c r="BC6" s="81">
+      <c r="BC6" s="69">
         <f t="shared" si="1"/>
         <v>46029</v>
       </c>
-      <c r="BD6" s="81">
+      <c r="BD6" s="69">
         <f t="shared" si="1"/>
         <v>46030</v>
       </c>
-      <c r="BE6" s="81">
+      <c r="BE6" s="69">
         <f t="shared" si="1"/>
         <v>46031</v>
       </c>
-      <c r="BF6" s="81">
+      <c r="BF6" s="69">
         <f t="shared" si="1"/>
         <v>46032</v>
       </c>
-      <c r="BG6" s="82">
+      <c r="BG6" s="70">
         <f t="shared" si="1"/>
         <v>46033</v>
       </c>
-      <c r="BH6" s="80">
+      <c r="BH6" s="68">
         <f t="shared" si="1"/>
         <v>46034</v>
       </c>
-      <c r="BI6" s="81">
+      <c r="BI6" s="69">
         <f t="shared" si="1"/>
         <v>46035</v>
       </c>
-      <c r="BJ6" s="81">
+      <c r="BJ6" s="69">
         <f t="shared" si="1"/>
         <v>46036</v>
       </c>
-      <c r="BK6" s="81">
+      <c r="BK6" s="69">
         <f t="shared" si="1"/>
         <v>46037</v>
       </c>
-      <c r="BL6" s="81">
+      <c r="BL6" s="69">
         <f t="shared" si="1"/>
         <v>46038</v>
       </c>
-      <c r="BM6" s="81">
+      <c r="BM6" s="69">
         <f t="shared" si="1"/>
         <v>46039</v>
       </c>
-      <c r="BN6" s="82">
+      <c r="BN6" s="70">
         <f t="shared" si="1"/>
         <v>46040</v>
       </c>
     </row>
-    <row r="7" ht="24.75" spans="1:66">
-      <c r="A7" s="83" t="s">
+    <row r="7" spans="1:66" ht="24">
+      <c r="A7" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="84" t="s">
+      <c r="C7" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="85" t="s">
+      <c r="D7" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="86" t="s">
+      <c r="E7" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="86" t="s">
+      <c r="F7" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="84" t="s">
+      <c r="G7" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="84" t="s">
+      <c r="H7" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="84" t="s">
+      <c r="I7" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="84"/>
-      <c r="K7" s="87" t="str">
+      <c r="J7" s="72"/>
+      <c r="K7" s="75" t="str">
         <f t="shared" ref="K7:AP7" si="2">CHOOSE(WEEKDAY(K6,1),"S","M","T","W","T","F","S")</f>
         <v>M</v>
       </c>
-      <c r="L7" s="88" t="str">
+      <c r="L7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>T</v>
       </c>
-      <c r="M7" s="88" t="str">
+      <c r="M7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>W</v>
       </c>
-      <c r="N7" s="88" t="str">
+      <c r="N7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>T</v>
       </c>
-      <c r="O7" s="88" t="str">
+      <c r="O7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>F</v>
       </c>
-      <c r="P7" s="88" t="str">
+      <c r="P7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>S</v>
       </c>
-      <c r="Q7" s="89" t="str">
+      <c r="Q7" s="77" t="str">
         <f t="shared" si="2"/>
         <v>S</v>
       </c>
-      <c r="R7" s="87" t="str">
+      <c r="R7" s="75" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
-      <c r="S7" s="88" t="str">
+      <c r="S7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>T</v>
       </c>
-      <c r="T7" s="88" t="str">
+      <c r="T7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>W</v>
       </c>
-      <c r="U7" s="88" t="str">
+      <c r="U7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>T</v>
       </c>
-      <c r="V7" s="88" t="str">
+      <c r="V7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>F</v>
       </c>
-      <c r="W7" s="88" t="str">
+      <c r="W7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>S</v>
       </c>
-      <c r="X7" s="89" t="str">
+      <c r="X7" s="77" t="str">
         <f t="shared" si="2"/>
         <v>S</v>
       </c>
-      <c r="Y7" s="87" t="str">
+      <c r="Y7" s="75" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
-      <c r="Z7" s="88" t="str">
+      <c r="Z7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>T</v>
       </c>
-      <c r="AA7" s="88" t="str">
+      <c r="AA7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>W</v>
       </c>
-      <c r="AB7" s="88" t="str">
+      <c r="AB7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>T</v>
       </c>
-      <c r="AC7" s="88" t="str">
+      <c r="AC7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>F</v>
       </c>
-      <c r="AD7" s="88" t="str">
+      <c r="AD7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>S</v>
       </c>
-      <c r="AE7" s="89" t="str">
+      <c r="AE7" s="77" t="str">
         <f t="shared" si="2"/>
         <v>S</v>
       </c>
-      <c r="AF7" s="87" t="str">
+      <c r="AF7" s="75" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
-      <c r="AG7" s="88" t="str">
+      <c r="AG7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>T</v>
       </c>
-      <c r="AH7" s="88" t="str">
+      <c r="AH7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>W</v>
       </c>
-      <c r="AI7" s="88" t="str">
+      <c r="AI7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>T</v>
       </c>
-      <c r="AJ7" s="88" t="str">
+      <c r="AJ7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>F</v>
       </c>
-      <c r="AK7" s="88" t="str">
+      <c r="AK7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>S</v>
       </c>
-      <c r="AL7" s="89" t="str">
+      <c r="AL7" s="77" t="str">
         <f t="shared" si="2"/>
         <v>S</v>
       </c>
-      <c r="AM7" s="87" t="str">
+      <c r="AM7" s="75" t="str">
         <f t="shared" si="2"/>
         <v>M</v>
       </c>
-      <c r="AN7" s="88" t="str">
+      <c r="AN7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>T</v>
       </c>
-      <c r="AO7" s="88" t="str">
+      <c r="AO7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>W</v>
       </c>
-      <c r="AP7" s="88" t="str">
+      <c r="AP7" s="76" t="str">
         <f t="shared" si="2"/>
         <v>T</v>
       </c>
-      <c r="AQ7" s="88" t="str">
+      <c r="AQ7" s="76" t="str">
         <f t="shared" ref="AQ7:BN7" si="3">CHOOSE(WEEKDAY(AQ6,1),"S","M","T","W","T","F","S")</f>
         <v>F</v>
       </c>
-      <c r="AR7" s="88" t="str">
+      <c r="AR7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="AS7" s="89" t="str">
+      <c r="AS7" s="77" t="str">
         <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="AT7" s="87" t="str">
+      <c r="AT7" s="75" t="str">
         <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="AU7" s="88" t="str">
+      <c r="AU7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>T</v>
       </c>
-      <c r="AV7" s="88" t="str">
+      <c r="AV7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>W</v>
       </c>
-      <c r="AW7" s="88" t="str">
+      <c r="AW7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>T</v>
       </c>
-      <c r="AX7" s="88" t="str">
+      <c r="AX7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>F</v>
       </c>
-      <c r="AY7" s="88" t="str">
+      <c r="AY7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="AZ7" s="89" t="str">
+      <c r="AZ7" s="77" t="str">
         <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="BA7" s="87" t="str">
+      <c r="BA7" s="75" t="str">
         <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="BB7" s="88" t="str">
+      <c r="BB7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>T</v>
       </c>
-      <c r="BC7" s="88" t="str">
+      <c r="BC7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>W</v>
       </c>
-      <c r="BD7" s="88" t="str">
+      <c r="BD7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>T</v>
       </c>
-      <c r="BE7" s="88" t="str">
+      <c r="BE7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>F</v>
       </c>
-      <c r="BF7" s="88" t="str">
+      <c r="BF7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="BG7" s="89" t="str">
+      <c r="BG7" s="77" t="str">
         <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="BH7" s="87" t="str">
+      <c r="BH7" s="75" t="str">
         <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="BI7" s="88" t="str">
+      <c r="BI7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>T</v>
       </c>
-      <c r="BJ7" s="88" t="str">
+      <c r="BJ7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>W</v>
       </c>
-      <c r="BK7" s="88" t="str">
+      <c r="BK7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>T</v>
       </c>
-      <c r="BL7" s="88" t="str">
+      <c r="BL7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>F</v>
       </c>
-      <c r="BM7" s="88" t="str">
+      <c r="BM7" s="76" t="str">
         <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="BN7" s="89" t="str">
+      <c r="BN7" s="77" t="str">
         <f t="shared" si="3"/>
         <v>S</v>
       </c>
     </row>
-    <row r="8" s="58" customFormat="1" ht="18" spans="1:66">
-      <c r="A8" s="90" t="str">
+    <row r="8" spans="1:66" s="55" customFormat="1" ht="18">
+      <c r="A8" s="78" t="str">
         <f>IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),TEXT(VALUE(prevWBS)+1,"#"),TEXT(VALUE(LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1))+1,"#")))</f>
         <v>1</v>
       </c>
-      <c r="B8" s="91" t="s">
+      <c r="B8" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="92"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="95" t="str">
+      <c r="C8" s="80"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="83" t="str">
         <f t="shared" ref="F8:F16" si="4">IF(ISBLANK(E8)," - ",IF(G8=0,E8,E8+G8-1))</f>
-        <v> - </v>
-      </c>
-      <c r="G8" s="96"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="98" t="str">
+        <v>-</v>
+      </c>
+      <c r="G8" s="84"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="86" t="str">
         <f>IF(OR(F8=0,E8=0)," - ",NETWORKDAYS(E8,F8))</f>
-        <v> - </v>
-      </c>
-      <c r="J8" s="99"/>
-      <c r="K8" s="100"/>
-      <c r="L8" s="100"/>
-      <c r="M8" s="100"/>
-      <c r="N8" s="100"/>
-      <c r="O8" s="100"/>
-      <c r="P8" s="100"/>
-      <c r="Q8" s="100"/>
-      <c r="R8" s="100"/>
-      <c r="S8" s="100"/>
-      <c r="T8" s="100"/>
-      <c r="U8" s="100"/>
-      <c r="V8" s="100"/>
-      <c r="W8" s="100"/>
-      <c r="X8" s="100"/>
-      <c r="Y8" s="100"/>
-      <c r="Z8" s="100"/>
-      <c r="AA8" s="100"/>
-      <c r="AB8" s="100"/>
-      <c r="AC8" s="100"/>
-      <c r="AD8" s="100"/>
-      <c r="AE8" s="100"/>
-      <c r="AF8" s="100"/>
-      <c r="AG8" s="100"/>
-      <c r="AH8" s="100"/>
-      <c r="AI8" s="100"/>
-      <c r="AJ8" s="100"/>
-      <c r="AK8" s="100"/>
-      <c r="AL8" s="100"/>
-      <c r="AM8" s="100"/>
-      <c r="AN8" s="100"/>
-      <c r="AO8" s="100"/>
-      <c r="AP8" s="100"/>
-      <c r="AQ8" s="100"/>
-      <c r="AR8" s="100"/>
-      <c r="AS8" s="100"/>
-      <c r="AT8" s="100"/>
-      <c r="AU8" s="100"/>
-      <c r="AV8" s="100"/>
-      <c r="AW8" s="100"/>
-      <c r="AX8" s="100"/>
-      <c r="AY8" s="100"/>
-      <c r="AZ8" s="100"/>
-      <c r="BA8" s="100"/>
-      <c r="BB8" s="100"/>
-      <c r="BC8" s="100"/>
-      <c r="BD8" s="100"/>
-      <c r="BE8" s="100"/>
-      <c r="BF8" s="100"/>
-      <c r="BG8" s="100"/>
-      <c r="BH8" s="100"/>
-      <c r="BI8" s="100"/>
-      <c r="BJ8" s="100"/>
-      <c r="BK8" s="100"/>
-      <c r="BL8" s="100"/>
-      <c r="BM8" s="100"/>
-      <c r="BN8" s="100"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="18" spans="1:66">
+        <v>-</v>
+      </c>
+      <c r="J8" s="87"/>
+      <c r="K8" s="88"/>
+      <c r="L8" s="88"/>
+      <c r="M8" s="88"/>
+      <c r="N8" s="88"/>
+      <c r="O8" s="88"/>
+      <c r="P8" s="88"/>
+      <c r="Q8" s="88"/>
+      <c r="R8" s="88"/>
+      <c r="S8" s="88"/>
+      <c r="T8" s="88"/>
+      <c r="U8" s="88"/>
+      <c r="V8" s="88"/>
+      <c r="W8" s="88"/>
+      <c r="X8" s="88"/>
+      <c r="Y8" s="88"/>
+      <c r="Z8" s="88"/>
+      <c r="AA8" s="88"/>
+      <c r="AB8" s="88"/>
+      <c r="AC8" s="88"/>
+      <c r="AD8" s="88"/>
+      <c r="AE8" s="88"/>
+      <c r="AF8" s="88"/>
+      <c r="AG8" s="88"/>
+      <c r="AH8" s="88"/>
+      <c r="AI8" s="88"/>
+      <c r="AJ8" s="88"/>
+      <c r="AK8" s="88"/>
+      <c r="AL8" s="88"/>
+      <c r="AM8" s="88"/>
+      <c r="AN8" s="88"/>
+      <c r="AO8" s="88"/>
+      <c r="AP8" s="88"/>
+      <c r="AQ8" s="88"/>
+      <c r="AR8" s="88"/>
+      <c r="AS8" s="88"/>
+      <c r="AT8" s="88"/>
+      <c r="AU8" s="88"/>
+      <c r="AV8" s="88"/>
+      <c r="AW8" s="88"/>
+      <c r="AX8" s="88"/>
+      <c r="AY8" s="88"/>
+      <c r="AZ8" s="88"/>
+      <c r="BA8" s="88"/>
+      <c r="BB8" s="88"/>
+      <c r="BC8" s="88"/>
+      <c r="BD8" s="88"/>
+      <c r="BE8" s="88"/>
+      <c r="BF8" s="88"/>
+      <c r="BG8" s="88"/>
+      <c r="BH8" s="88"/>
+      <c r="BI8" s="88"/>
+      <c r="BJ8" s="88"/>
+      <c r="BK8" s="88"/>
+      <c r="BL8" s="88"/>
+      <c r="BM8" s="88"/>
+      <c r="BN8" s="88"/>
+    </row>
+    <row r="9" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A9" s="4" t="str">
         <f t="shared" ref="A9:A19" si="5">IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"0.1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),prevWBS&amp;".1",LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1)))&amp;IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",2))),VALUE(RIGHT(prevWBS,LEN(prevWBS)-FIND("`",SUBSTITUTE(prevWBS,".","`",1))))+1,VALUE(MID(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))+1,(FIND("`",SUBSTITUTE(prevWBS,".","`",2))-FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1)))+1)))</f>
         <v>1.1</v>
       </c>
-      <c r="B9" s="101" t="s">
+      <c r="B9" s="89" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -5650,12 +5097,12 @@
       <c r="BM9" s="4"/>
       <c r="BN9" s="4"/>
     </row>
-    <row r="10" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="10" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A10" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.2</v>
       </c>
-      <c r="B10" s="101" t="s">
+      <c r="B10" s="89" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -5737,12 +5184,12 @@
       <c r="BM10" s="4"/>
       <c r="BN10" s="4"/>
     </row>
-    <row r="11" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="11" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A11" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.3</v>
       </c>
-      <c r="B11" s="101" t="s">
+      <c r="B11" s="89" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -5824,12 +5271,12 @@
       <c r="BM11" s="4"/>
       <c r="BN11" s="4"/>
     </row>
-    <row r="12" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="12" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A12" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.4</v>
       </c>
-      <c r="B12" s="101" t="s">
+      <c r="B12" s="89" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -5911,12 +5358,12 @@
       <c r="BM12" s="4"/>
       <c r="BN12" s="4"/>
     </row>
-    <row r="13" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="13" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A13" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
-      <c r="B13" s="101" t="s">
+      <c r="B13" s="89" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -5998,12 +5445,12 @@
       <c r="BM13" s="4"/>
       <c r="BN13" s="4"/>
     </row>
-    <row r="14" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="14" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A14" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.6</v>
       </c>
-      <c r="B14" s="101" t="s">
+      <c r="B14" s="89" t="s">
         <v>22</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -6085,12 +5532,12 @@
       <c r="BM14" s="4"/>
       <c r="BN14" s="4"/>
     </row>
-    <row r="15" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="15" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A15" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.7</v>
       </c>
-      <c r="B15" s="101" t="s">
+      <c r="B15" s="89" t="s">
         <v>23</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -6172,12 +5619,12 @@
       <c r="BM15" s="4"/>
       <c r="BN15" s="4"/>
     </row>
-    <row r="16" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="16" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A16" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.8</v>
       </c>
-      <c r="B16" s="101" t="s">
+      <c r="B16" s="89" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -6259,12 +5706,12 @@
       <c r="BM16" s="4"/>
       <c r="BN16" s="4"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="17" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A17" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.9</v>
       </c>
-      <c r="B17" s="101" t="s">
+      <c r="B17" s="89" t="s">
         <v>26</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -6346,12 +5793,12 @@
       <c r="BM17" s="4"/>
       <c r="BN17" s="4"/>
     </row>
-    <row r="18" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="18" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A18" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.10</v>
       </c>
-      <c r="B18" s="101" t="s">
+      <c r="B18" s="89" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -6433,12 +5880,12 @@
       <c r="BM18" s="4"/>
       <c r="BN18" s="4"/>
     </row>
-    <row r="19" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="19" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A19" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.11</v>
       </c>
-      <c r="B19" s="101" t="s">
+      <c r="B19" s="89" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -6520,12 +5967,12 @@
       <c r="BM19" s="4"/>
       <c r="BN19" s="4"/>
     </row>
-    <row r="20" s="1" customFormat="1" ht="21" customHeight="1" spans="1:66">
+    <row r="20" spans="1:66" s="1" customFormat="1" ht="21" customHeight="1">
       <c r="A20" s="4" t="str">
         <f t="shared" ref="A20:A60" si="14">IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"0.1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),prevWBS&amp;".1",LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1)))&amp;IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",2))),VALUE(RIGHT(prevWBS,LEN(prevWBS)-FIND("`",SUBSTITUTE(prevWBS,".","`",1))))+1,VALUE(MID(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))+1,(FIND("`",SUBSTITUTE(prevWBS,".","`",2))-FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1)))+1)))</f>
         <v>1.12</v>
       </c>
-      <c r="B20" s="101" t="s">
+      <c r="B20" s="89" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -6607,12 +6054,12 @@
       <c r="BM20" s="4"/>
       <c r="BN20" s="4"/>
     </row>
-    <row r="21" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="21" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A21" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.13</v>
       </c>
-      <c r="B21" s="101" t="s">
+      <c r="B21" s="89" t="s">
         <v>31</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -6694,12 +6141,12 @@
       <c r="BM21" s="4"/>
       <c r="BN21" s="4"/>
     </row>
-    <row r="22" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="22" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A22" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.14</v>
       </c>
-      <c r="B22" s="102" t="s">
+      <c r="B22" s="90" t="s">
         <v>32</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -6781,12 +6228,12 @@
       <c r="BM22" s="4"/>
       <c r="BN22" s="4"/>
     </row>
-    <row r="23" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="23" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A23" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.15</v>
       </c>
-      <c r="B23" s="101" t="s">
+      <c r="B23" s="89" t="s">
         <v>33</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -6868,12 +6315,12 @@
       <c r="BM23" s="4"/>
       <c r="BN23" s="4"/>
     </row>
-    <row r="24" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="24" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A24" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.16</v>
       </c>
-      <c r="B24" s="101" t="s">
+      <c r="B24" s="89" t="s">
         <v>34</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -6956,12 +6403,12 @@
       <c r="BM24" s="4"/>
       <c r="BN24" s="4"/>
     </row>
-    <row r="25" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="25" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A25" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.17</v>
       </c>
-      <c r="B25" s="101" t="s">
+      <c r="B25" s="89" t="s">
         <v>35</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -7044,12 +6491,12 @@
       <c r="BM25" s="4"/>
       <c r="BN25" s="4"/>
     </row>
-    <row r="26" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="26" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A26" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.18</v>
       </c>
-      <c r="B26" s="101" t="s">
+      <c r="B26" s="89" t="s">
         <v>36</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -7132,12 +6579,12 @@
       <c r="BM26" s="4"/>
       <c r="BN26" s="4"/>
     </row>
-    <row r="27" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="27" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A27" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.19</v>
       </c>
-      <c r="B27" s="101" t="s">
+      <c r="B27" s="89" t="s">
         <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -7220,12 +6667,12 @@
       <c r="BM27" s="4"/>
       <c r="BN27" s="4"/>
     </row>
-    <row r="28" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="28" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A28" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.20</v>
       </c>
-      <c r="B28" s="101" t="s">
+      <c r="B28" s="89" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -7308,12 +6755,12 @@
       <c r="BM28" s="4"/>
       <c r="BN28" s="4"/>
     </row>
-    <row r="29" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="29" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A29" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.21</v>
       </c>
-      <c r="B29" s="101" t="s">
+      <c r="B29" s="89" t="s">
         <v>39</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -7396,12 +6843,12 @@
       <c r="BM29" s="4"/>
       <c r="BN29" s="4"/>
     </row>
-    <row r="30" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="30" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A30" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.22</v>
       </c>
-      <c r="B30" s="101" t="s">
+      <c r="B30" s="89" t="s">
         <v>40</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -7484,12 +6931,12 @@
       <c r="BM30" s="4"/>
       <c r="BN30" s="4"/>
     </row>
-    <row r="31" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="31" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A31" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.23</v>
       </c>
-      <c r="B31" s="101" t="s">
+      <c r="B31" s="89" t="s">
         <v>41</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -7572,12 +7019,12 @@
       <c r="BM31" s="4"/>
       <c r="BN31" s="4"/>
     </row>
-    <row r="32" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="32" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A32" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.24</v>
       </c>
-      <c r="B32" s="101" t="s">
+      <c r="B32" s="89" t="s">
         <v>42</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -7660,12 +7107,12 @@
       <c r="BM32" s="4"/>
       <c r="BN32" s="4"/>
     </row>
-    <row r="33" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="33" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A33" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.25</v>
       </c>
-      <c r="B33" s="103" t="s">
+      <c r="B33" s="91" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -7748,12 +7195,12 @@
       <c r="BM33" s="4"/>
       <c r="BN33" s="4"/>
     </row>
-    <row r="34" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="34" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A34" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.26</v>
       </c>
-      <c r="B34" s="104" t="s">
+      <c r="B34" s="92" t="s">
         <v>44</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -7836,16 +7283,16 @@
       <c r="BM34" s="4"/>
       <c r="BN34" s="4"/>
     </row>
-    <row r="35" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="35" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A35" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.27</v>
       </c>
-      <c r="B35" s="105" t="s">
+      <c r="B35" s="93" t="s">
         <v>45</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="6">
@@ -7924,16 +7371,16 @@
       <c r="BM35" s="4"/>
       <c r="BN35" s="4"/>
     </row>
-    <row r="36" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="36" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A36" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.28</v>
       </c>
-      <c r="B36" s="106" t="s">
-        <v>47</v>
+      <c r="B36" s="94" t="s">
+        <v>46</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="6">
@@ -8012,16 +7459,16 @@
       <c r="BM36" s="4"/>
       <c r="BN36" s="4"/>
     </row>
-    <row r="37" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="37" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A37" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.29</v>
       </c>
-      <c r="B37" s="106" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" s="107" t="s">
-        <v>46</v>
+      <c r="B37" s="94" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="95" t="s">
+        <v>55</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="6">
@@ -8100,16 +7547,16 @@
       <c r="BM37" s="4"/>
       <c r="BN37" s="4"/>
     </row>
-    <row r="38" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="38" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A38" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.30</v>
       </c>
-      <c r="B38" s="105" t="s">
-        <v>50</v>
+      <c r="B38" s="93" t="s">
+        <v>48</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="6">
@@ -8188,16 +7635,16 @@
       <c r="BM38" s="4"/>
       <c r="BN38" s="4"/>
     </row>
-    <row r="39" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="39" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A39" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.31</v>
       </c>
-      <c r="B39" s="105" t="s">
-        <v>52</v>
+      <c r="B39" s="93" t="s">
+        <v>49</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="6">
@@ -8276,16 +7723,16 @@
       <c r="BM39" s="4"/>
       <c r="BN39" s="4"/>
     </row>
-    <row r="40" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="40" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A40" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.32</v>
       </c>
-      <c r="B40" s="106" t="s">
-        <v>53</v>
+      <c r="B40" s="94" t="s">
+        <v>50</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="6">
@@ -8364,16 +7811,16 @@
       <c r="BM40" s="4"/>
       <c r="BN40" s="4"/>
     </row>
-    <row r="41" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="41" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A41" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.33</v>
       </c>
-      <c r="B41" s="105" t="s">
-        <v>54</v>
+      <c r="B41" s="93" t="s">
+        <v>51</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="6">
@@ -8387,7 +7834,7 @@
       <c r="G41" s="8">
         <v>4</v>
       </c>
-      <c r="H41" s="108">
+      <c r="H41" s="96">
         <v>1</v>
       </c>
       <c r="I41" s="10">
@@ -8452,16 +7899,16 @@
       <c r="BM41" s="4"/>
       <c r="BN41" s="4"/>
     </row>
-    <row r="42" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="42" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A42" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.34</v>
       </c>
-      <c r="B42" s="105" t="s">
-        <v>56</v>
+      <c r="B42" s="93" t="s">
+        <v>53</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="6">
@@ -8540,16 +7987,16 @@
       <c r="BM42" s="4"/>
       <c r="BN42" s="4"/>
     </row>
-    <row r="43" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="43" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A43" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.35</v>
       </c>
-      <c r="B43" s="106" t="s">
-        <v>57</v>
-      </c>
-      <c r="C43" s="109" t="s">
-        <v>58</v>
+      <c r="B43" s="94" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="97" t="s">
+        <v>55</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="6">
@@ -8628,16 +8075,16 @@
       <c r="BM43" s="4"/>
       <c r="BN43" s="4"/>
     </row>
-    <row r="44" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="44" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A44" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.36</v>
       </c>
-      <c r="B44" s="110" t="s">
-        <v>59</v>
-      </c>
-      <c r="C44" s="109" t="s">
-        <v>55</v>
+      <c r="B44" s="98" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="97" t="s">
+        <v>52</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="6">
@@ -8716,16 +8163,16 @@
       <c r="BM44" s="4"/>
       <c r="BN44" s="4"/>
     </row>
-    <row r="45" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="45" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A45" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.37</v>
       </c>
-      <c r="B45" s="101" t="s">
-        <v>60</v>
+      <c r="B45" s="89" t="s">
+        <v>57</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="6">
@@ -8804,13 +8251,13 @@
       <c r="BM45" s="4"/>
       <c r="BN45" s="4"/>
     </row>
-    <row r="46" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="46" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A46" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.38</v>
       </c>
-      <c r="B46" s="105" t="s">
-        <v>61</v>
+      <c r="B46" s="93" t="s">
+        <v>58</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -8892,13 +8339,13 @@
       <c r="BM46" s="4"/>
       <c r="BN46" s="4"/>
     </row>
-    <row r="47" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="47" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A47" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.39</v>
       </c>
-      <c r="B47" s="105" t="s">
-        <v>62</v>
+      <c r="B47" s="93" t="s">
+        <v>59</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>20</v>
@@ -8980,13 +8427,13 @@
       <c r="BM47" s="4"/>
       <c r="BN47" s="4"/>
     </row>
-    <row r="48" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="48" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A48" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.40</v>
       </c>
-      <c r="B48" s="111" t="s">
-        <v>63</v>
+      <c r="B48" s="99" t="s">
+        <v>60</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>29</v>
@@ -9068,16 +8515,16 @@
       <c r="BM48" s="4"/>
       <c r="BN48" s="4"/>
     </row>
-    <row r="49" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="49" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A49" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.41</v>
       </c>
-      <c r="B49" s="105" t="s">
-        <v>64</v>
+      <c r="B49" s="93" t="s">
+        <v>61</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="6">
@@ -9156,16 +8603,16 @@
       <c r="BM49" s="4"/>
       <c r="BN49" s="4"/>
     </row>
-    <row r="50" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="50" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A50" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.42</v>
       </c>
-      <c r="B50" s="105" t="s">
-        <v>65</v>
+      <c r="B50" s="93" t="s">
+        <v>62</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="6">
@@ -9244,16 +8691,16 @@
       <c r="BM50" s="4"/>
       <c r="BN50" s="4"/>
     </row>
-    <row r="51" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="51" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A51" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.43</v>
       </c>
-      <c r="B51" s="105" t="s">
-        <v>67</v>
+      <c r="B51" s="93" t="s">
+        <v>63</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="6">
@@ -9332,16 +8779,16 @@
       <c r="BM51" s="4"/>
       <c r="BN51" s="4"/>
     </row>
-    <row r="52" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="52" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A52" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.44</v>
       </c>
-      <c r="B52" s="110" t="s">
-        <v>68</v>
+      <c r="B52" s="98" t="s">
+        <v>64</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="6">
@@ -9420,16 +8867,16 @@
       <c r="BM52" s="4"/>
       <c r="BN52" s="4"/>
     </row>
-    <row r="53" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="53" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A53" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.45</v>
       </c>
-      <c r="B53" s="110" t="s">
-        <v>69</v>
+      <c r="B53" s="98" t="s">
+        <v>65</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="6">
@@ -9508,28 +8955,28 @@
       <c r="BM53" s="4"/>
       <c r="BN53" s="4"/>
     </row>
-    <row r="54" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="54" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A54" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.46</v>
       </c>
-      <c r="B54" s="110" t="s">
-        <v>70</v>
+      <c r="B54" s="98" t="s">
+        <v>66</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="6">
-        <f t="shared" si="37"/>
-        <v>46099</v>
+        <f>F52+10</f>
+        <v>46108</v>
       </c>
       <c r="F54" s="7">
         <f t="shared" si="33"/>
-        <v>46100</v>
+        <v>46111</v>
       </c>
       <c r="G54" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H54" s="9">
         <v>0</v>
@@ -9596,28 +9043,28 @@
       <c r="BM54" s="4"/>
       <c r="BN54" s="4"/>
     </row>
-    <row r="55" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="55" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A55" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.47</v>
       </c>
-      <c r="B55" s="110" t="s">
-        <v>71</v>
+      <c r="B55" s="98" t="s">
+        <v>67</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="6">
-        <f t="shared" si="37"/>
-        <v>46099</v>
+        <f>F53+10</f>
+        <v>46108</v>
       </c>
       <c r="F55" s="7">
         <f t="shared" si="33"/>
-        <v>46100</v>
+        <v>46111</v>
       </c>
       <c r="G55" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H55" s="9">
         <v>0</v>
@@ -9684,28 +9131,28 @@
       <c r="BM55" s="4"/>
       <c r="BN55" s="4"/>
     </row>
-    <row r="56" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="56" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A56" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.48</v>
       </c>
-      <c r="B56" s="110" t="s">
-        <v>72</v>
+      <c r="B56" s="98" t="s">
+        <v>68</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="6">
-        <f>F54+9</f>
-        <v>46109</v>
+        <f>F54+1</f>
+        <v>46112</v>
       </c>
       <c r="F56" s="7">
         <f t="shared" si="33"/>
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="G56" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H56" s="9">
         <v>0</v>
@@ -9772,28 +9219,28 @@
       <c r="BM56" s="4"/>
       <c r="BN56" s="4"/>
     </row>
-    <row r="57" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="57" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A57" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.49</v>
       </c>
-      <c r="B57" s="105" t="s">
-        <v>73</v>
+      <c r="B57" s="93" t="s">
+        <v>69</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="6">
-        <f>F55+9</f>
-        <v>46109</v>
+        <f>F55+1</f>
+        <v>46112</v>
       </c>
       <c r="F57" s="7">
         <f t="shared" si="33"/>
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="G57" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H57" s="9">
         <v>0</v>
@@ -9860,25 +9307,25 @@
       <c r="BM57" s="4"/>
       <c r="BN57" s="4"/>
     </row>
-    <row r="58" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="58" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A58" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.50</v>
       </c>
-      <c r="B58" s="110" t="s">
-        <v>74</v>
+      <c r="B58" s="98" t="s">
+        <v>70</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="6">
         <f>F56+1</f>
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="F58" s="7">
         <f t="shared" si="33"/>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="G58" s="8">
         <v>2</v>
@@ -9948,25 +9395,25 @@
       <c r="BM58" s="4"/>
       <c r="BN58" s="4"/>
     </row>
-    <row r="59" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="59" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A59" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.51</v>
       </c>
-      <c r="B59" s="106" t="s">
-        <v>75</v>
-      </c>
-      <c r="C59" s="107" t="s">
-        <v>48</v>
+      <c r="B59" s="94" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59" s="95" t="s">
+        <v>55</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="6">
         <f>F57+1</f>
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="F59" s="7">
         <f t="shared" si="33"/>
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="G59" s="8">
         <v>2</v>
@@ -10036,25 +9483,25 @@
       <c r="BM59" s="4"/>
       <c r="BN59" s="4"/>
     </row>
-    <row r="60" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="60" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A60" s="4" t="str">
         <f t="shared" si="14"/>
         <v>1.52</v>
       </c>
-      <c r="B60" s="105" t="s">
-        <v>76</v>
+      <c r="B60" s="93" t="s">
+        <v>72</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="6">
         <f>F58+1</f>
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="F60" s="7">
         <f t="shared" si="33"/>
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="G60" s="8">
         <v>4</v>
@@ -10124,14 +9571,14 @@
       <c r="BM60" s="4"/>
       <c r="BN60" s="4"/>
     </row>
-    <row r="62" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="62" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A62" s="4"/>
-      <c r="B62" s="105"/>
+      <c r="B62" s="93"/>
       <c r="D62" s="5"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="9"/>
+      <c r="E62" s="122"/>
+      <c r="F62" s="123"/>
+      <c r="G62" s="124"/>
+      <c r="H62" s="125"/>
       <c r="I62" s="10"/>
       <c r="J62" s="11"/>
       <c r="K62" s="4"/>
@@ -10191,14 +9638,14 @@
       <c r="BM62" s="4"/>
       <c r="BN62" s="4"/>
     </row>
-    <row r="63" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="63" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A63" s="4"/>
-      <c r="B63" s="105"/>
+      <c r="B63" s="93"/>
       <c r="D63" s="5"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="9"/>
+      <c r="E63" s="122"/>
+      <c r="F63" s="123"/>
+      <c r="G63" s="124"/>
+      <c r="H63" s="125"/>
       <c r="I63" s="10"/>
       <c r="J63" s="11"/>
       <c r="K63" s="4"/>
@@ -10258,14 +9705,14 @@
       <c r="BM63" s="4"/>
       <c r="BN63" s="4"/>
     </row>
-    <row r="64" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="64" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A64" s="4"/>
-      <c r="B64" s="105"/>
+      <c r="B64" s="93"/>
       <c r="D64" s="5"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="9"/>
+      <c r="E64" s="122"/>
+      <c r="F64" s="123"/>
+      <c r="G64" s="124"/>
+      <c r="H64" s="125"/>
       <c r="I64" s="10"/>
       <c r="J64" s="11"/>
       <c r="K64" s="4"/>
@@ -10325,14 +9772,14 @@
       <c r="BM64" s="4"/>
       <c r="BN64" s="4"/>
     </row>
-    <row r="65" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="65" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A65" s="4"/>
-      <c r="B65" s="105"/>
+      <c r="B65" s="93"/>
       <c r="D65" s="5"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="9"/>
+      <c r="E65" s="122"/>
+      <c r="F65" s="123"/>
+      <c r="G65" s="124"/>
+      <c r="H65" s="125"/>
       <c r="I65" s="10"/>
       <c r="J65" s="11"/>
       <c r="K65" s="4"/>
@@ -10392,14 +9839,14 @@
       <c r="BM65" s="4"/>
       <c r="BN65" s="4"/>
     </row>
-    <row r="66" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="66" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A66" s="4"/>
-      <c r="B66" s="105"/>
+      <c r="B66" s="93"/>
       <c r="D66" s="5"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="9"/>
+      <c r="E66" s="122"/>
+      <c r="F66" s="123"/>
+      <c r="G66" s="124"/>
+      <c r="H66" s="125"/>
       <c r="I66" s="10"/>
       <c r="J66" s="11"/>
       <c r="K66" s="4"/>
@@ -10459,14 +9906,14 @@
       <c r="BM66" s="4"/>
       <c r="BN66" s="4"/>
     </row>
-    <row r="67" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="67" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A67" s="4"/>
-      <c r="B67" s="105"/>
+      <c r="B67" s="93"/>
       <c r="D67" s="5"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="9"/>
+      <c r="E67" s="122"/>
+      <c r="F67" s="123"/>
+      <c r="G67" s="124"/>
+      <c r="H67" s="125"/>
       <c r="I67" s="10"/>
       <c r="J67" s="11"/>
       <c r="K67" s="4"/>
@@ -10526,14 +9973,14 @@
       <c r="BM67" s="4"/>
       <c r="BN67" s="4"/>
     </row>
-    <row r="68" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="68" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A68" s="4"/>
-      <c r="B68" s="105"/>
+      <c r="B68" s="93"/>
       <c r="D68" s="5"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="9"/>
+      <c r="E68" s="122"/>
+      <c r="F68" s="123"/>
+      <c r="G68" s="124"/>
+      <c r="H68" s="125"/>
       <c r="I68" s="10"/>
       <c r="J68" s="11"/>
       <c r="K68" s="4"/>
@@ -10593,14 +10040,14 @@
       <c r="BM68" s="4"/>
       <c r="BN68" s="4"/>
     </row>
-    <row r="69" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="69" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A69" s="4"/>
-      <c r="B69" s="105"/>
+      <c r="B69" s="93"/>
       <c r="D69" s="5"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="9"/>
+      <c r="E69" s="122"/>
+      <c r="F69" s="123"/>
+      <c r="G69" s="124"/>
+      <c r="H69" s="125"/>
       <c r="I69" s="10"/>
       <c r="J69" s="11"/>
       <c r="K69" s="4"/>
@@ -10660,14 +10107,14 @@
       <c r="BM69" s="4"/>
       <c r="BN69" s="4"/>
     </row>
-    <row r="70" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="70" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A70" s="4"/>
-      <c r="B70" s="105"/>
+      <c r="B70" s="93"/>
       <c r="D70" s="5"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="9"/>
+      <c r="E70" s="122"/>
+      <c r="F70" s="123"/>
+      <c r="G70" s="124"/>
+      <c r="H70" s="125"/>
       <c r="I70" s="10"/>
       <c r="J70" s="11"/>
       <c r="K70" s="4"/>
@@ -10727,14 +10174,14 @@
       <c r="BM70" s="4"/>
       <c r="BN70" s="4"/>
     </row>
-    <row r="71" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="71" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A71" s="4"/>
-      <c r="B71" s="105"/>
+      <c r="B71" s="93"/>
       <c r="D71" s="5"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="9"/>
+      <c r="E71" s="122"/>
+      <c r="F71" s="123"/>
+      <c r="G71" s="124"/>
+      <c r="H71" s="125"/>
       <c r="I71" s="10"/>
       <c r="J71" s="11"/>
       <c r="K71" s="4"/>
@@ -10794,14 +10241,14 @@
       <c r="BM71" s="4"/>
       <c r="BN71" s="4"/>
     </row>
-    <row r="72" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="72" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A72" s="4"/>
-      <c r="B72" s="105"/>
+      <c r="B72" s="93"/>
       <c r="D72" s="5"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="9"/>
+      <c r="E72" s="122"/>
+      <c r="F72" s="123"/>
+      <c r="G72" s="124"/>
+      <c r="H72" s="125"/>
       <c r="I72" s="10"/>
       <c r="J72" s="11"/>
       <c r="K72" s="4"/>
@@ -10861,14 +10308,14 @@
       <c r="BM72" s="4"/>
       <c r="BN72" s="4"/>
     </row>
-    <row r="73" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="73" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A73" s="4"/>
-      <c r="B73" s="105"/>
+      <c r="B73" s="93"/>
       <c r="D73" s="5"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="9"/>
+      <c r="E73" s="122"/>
+      <c r="F73" s="123"/>
+      <c r="G73" s="124"/>
+      <c r="H73" s="125"/>
       <c r="I73" s="10"/>
       <c r="J73" s="11"/>
       <c r="K73" s="4"/>
@@ -10928,14 +10375,14 @@
       <c r="BM73" s="4"/>
       <c r="BN73" s="4"/>
     </row>
-    <row r="74" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="74" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A74" s="4"/>
-      <c r="B74" s="105"/>
+      <c r="B74" s="93"/>
       <c r="D74" s="5"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="9"/>
+      <c r="E74" s="122"/>
+      <c r="F74" s="123"/>
+      <c r="G74" s="124"/>
+      <c r="H74" s="125"/>
       <c r="I74" s="10"/>
       <c r="J74" s="11"/>
       <c r="K74" s="4"/>
@@ -10995,14 +10442,14 @@
       <c r="BM74" s="4"/>
       <c r="BN74" s="4"/>
     </row>
-    <row r="75" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="75" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A75" s="4"/>
-      <c r="B75" s="105"/>
+      <c r="B75" s="93"/>
       <c r="D75" s="5"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="9"/>
+      <c r="E75" s="122"/>
+      <c r="F75" s="123"/>
+      <c r="G75" s="124"/>
+      <c r="H75" s="125"/>
       <c r="I75" s="10"/>
       <c r="J75" s="11"/>
       <c r="K75" s="4"/>
@@ -11062,94 +10509,94 @@
       <c r="BM75" s="4"/>
       <c r="BN75" s="4"/>
     </row>
-    <row r="76" s="58" customFormat="1" ht="18" hidden="1" spans="1:66">
-      <c r="A76" s="112" t="str">
+    <row r="76" spans="1:66" s="55" customFormat="1" ht="18" hidden="1">
+      <c r="A76" s="100" t="str">
         <f>IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),TEXT(VALUE(prevWBS)+1,"#"),TEXT(VALUE(LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1))+1,"#")))</f>
         <v>1</v>
       </c>
-      <c r="B76" s="113" t="s">
-        <v>77</v>
-      </c>
-      <c r="D76" s="114"/>
-      <c r="E76" s="115"/>
-      <c r="F76" s="115" t="str">
+      <c r="B76" s="101" t="s">
+        <v>73</v>
+      </c>
+      <c r="D76" s="102"/>
+      <c r="E76" s="103"/>
+      <c r="F76" s="103" t="str">
         <f t="shared" ref="F76:F81" si="38">IF(ISBLANK(E76)," - ",IF(G76=0,E76,E76+G76-1))</f>
-        <v> - </v>
-      </c>
-      <c r="G76" s="116"/>
-      <c r="H76" s="117"/>
-      <c r="I76" s="118" t="str">
+        <v>-</v>
+      </c>
+      <c r="G76" s="104"/>
+      <c r="H76" s="105"/>
+      <c r="I76" s="106" t="str">
         <f t="shared" ref="I76:I81" si="39">IF(OR(F76=0,E76=0)," - ",NETWORKDAYS(E76,F76))</f>
-        <v> - </v>
-      </c>
-      <c r="J76" s="119"/>
-      <c r="K76" s="120"/>
-      <c r="L76" s="120"/>
-      <c r="M76" s="120"/>
-      <c r="N76" s="120"/>
-      <c r="O76" s="120"/>
-      <c r="P76" s="120"/>
-      <c r="Q76" s="120"/>
-      <c r="R76" s="120"/>
-      <c r="S76" s="120"/>
-      <c r="T76" s="120"/>
-      <c r="U76" s="120"/>
-      <c r="V76" s="120"/>
-      <c r="W76" s="120"/>
-      <c r="X76" s="120"/>
-      <c r="Y76" s="120"/>
-      <c r="Z76" s="120"/>
-      <c r="AA76" s="120"/>
-      <c r="AB76" s="120"/>
-      <c r="AC76" s="120"/>
-      <c r="AD76" s="120"/>
-      <c r="AE76" s="120"/>
-      <c r="AF76" s="120"/>
-      <c r="AG76" s="120"/>
-      <c r="AH76" s="120"/>
-      <c r="AI76" s="120"/>
-      <c r="AJ76" s="120"/>
-      <c r="AK76" s="120"/>
-      <c r="AL76" s="120"/>
-      <c r="AM76" s="120"/>
-      <c r="AN76" s="120"/>
-      <c r="AO76" s="120"/>
-      <c r="AP76" s="120"/>
-      <c r="AQ76" s="120"/>
-      <c r="AR76" s="120"/>
-      <c r="AS76" s="120"/>
-      <c r="AT76" s="120"/>
-      <c r="AU76" s="120"/>
-      <c r="AV76" s="120"/>
-      <c r="AW76" s="120"/>
-      <c r="AX76" s="120"/>
-      <c r="AY76" s="120"/>
-      <c r="AZ76" s="120"/>
-      <c r="BA76" s="120"/>
-      <c r="BB76" s="120"/>
-      <c r="BC76" s="120"/>
-      <c r="BD76" s="120"/>
-      <c r="BE76" s="120"/>
-      <c r="BF76" s="120"/>
-      <c r="BG76" s="120"/>
-      <c r="BH76" s="120"/>
-      <c r="BI76" s="120"/>
-      <c r="BJ76" s="120"/>
-      <c r="BK76" s="120"/>
-      <c r="BL76" s="120"/>
-      <c r="BM76" s="120"/>
-      <c r="BN76" s="120"/>
-    </row>
-    <row r="77" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+        <v>-</v>
+      </c>
+      <c r="J76" s="107"/>
+      <c r="K76" s="108"/>
+      <c r="L76" s="108"/>
+      <c r="M76" s="108"/>
+      <c r="N76" s="108"/>
+      <c r="O76" s="108"/>
+      <c r="P76" s="108"/>
+      <c r="Q76" s="108"/>
+      <c r="R76" s="108"/>
+      <c r="S76" s="108"/>
+      <c r="T76" s="108"/>
+      <c r="U76" s="108"/>
+      <c r="V76" s="108"/>
+      <c r="W76" s="108"/>
+      <c r="X76" s="108"/>
+      <c r="Y76" s="108"/>
+      <c r="Z76" s="108"/>
+      <c r="AA76" s="108"/>
+      <c r="AB76" s="108"/>
+      <c r="AC76" s="108"/>
+      <c r="AD76" s="108"/>
+      <c r="AE76" s="108"/>
+      <c r="AF76" s="108"/>
+      <c r="AG76" s="108"/>
+      <c r="AH76" s="108"/>
+      <c r="AI76" s="108"/>
+      <c r="AJ76" s="108"/>
+      <c r="AK76" s="108"/>
+      <c r="AL76" s="108"/>
+      <c r="AM76" s="108"/>
+      <c r="AN76" s="108"/>
+      <c r="AO76" s="108"/>
+      <c r="AP76" s="108"/>
+      <c r="AQ76" s="108"/>
+      <c r="AR76" s="108"/>
+      <c r="AS76" s="108"/>
+      <c r="AT76" s="108"/>
+      <c r="AU76" s="108"/>
+      <c r="AV76" s="108"/>
+      <c r="AW76" s="108"/>
+      <c r="AX76" s="108"/>
+      <c r="AY76" s="108"/>
+      <c r="AZ76" s="108"/>
+      <c r="BA76" s="108"/>
+      <c r="BB76" s="108"/>
+      <c r="BC76" s="108"/>
+      <c r="BD76" s="108"/>
+      <c r="BE76" s="108"/>
+      <c r="BF76" s="108"/>
+      <c r="BG76" s="108"/>
+      <c r="BH76" s="108"/>
+      <c r="BI76" s="108"/>
+      <c r="BJ76" s="108"/>
+      <c r="BK76" s="108"/>
+      <c r="BL76" s="108"/>
+      <c r="BM76" s="108"/>
+      <c r="BN76" s="108"/>
+    </row>
+    <row r="77" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A77" s="4" t="str">
         <f t="shared" ref="A77:A115" si="40">IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"0.1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),prevWBS&amp;".1",LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1)))&amp;IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",2))),VALUE(RIGHT(prevWBS,LEN(prevWBS)-FIND("`",SUBSTITUTE(prevWBS,".","`",1))))+1,VALUE(MID(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))+1,(FIND("`",SUBSTITUTE(prevWBS,".","`",2))-FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1)))+1)))</f>
         <v>1.1</v>
       </c>
-      <c r="B77" s="105" t="s">
-        <v>78</v>
+      <c r="B77" s="93" t="s">
+        <v>74</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="6">
@@ -11227,13 +10674,13 @@
       <c r="BM77" s="4"/>
       <c r="BN77" s="4"/>
     </row>
-    <row r="78" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="78" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A78" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.2</v>
       </c>
-      <c r="B78" s="105" t="s">
-        <v>80</v>
+      <c r="B78" s="93" t="s">
+        <v>76</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>20</v>
@@ -11314,13 +10761,13 @@
       <c r="BM78" s="4"/>
       <c r="BN78" s="4"/>
     </row>
-    <row r="79" s="1" customFormat="1" ht="44.25" hidden="1" customHeight="1" spans="1:66">
+    <row r="79" spans="1:66" s="1" customFormat="1" ht="44.25" hidden="1" customHeight="1">
       <c r="A79" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.3</v>
       </c>
-      <c r="B79" s="105" t="s">
-        <v>81</v>
+      <c r="B79" s="93" t="s">
+        <v>77</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>29</v>
@@ -11401,13 +10848,13 @@
       <c r="BM79" s="4"/>
       <c r="BN79" s="4"/>
     </row>
-    <row r="80" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="80" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A80" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.4</v>
       </c>
-      <c r="B80" s="105" t="s">
-        <v>82</v>
+      <c r="B80" s="93" t="s">
+        <v>78</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>20</v>
@@ -11488,13 +10935,13 @@
       <c r="BM80" s="4"/>
       <c r="BN80" s="4"/>
     </row>
-    <row r="81" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="81" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A81" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.5</v>
       </c>
-      <c r="B81" s="105" t="s">
-        <v>83</v>
+      <c r="B81" s="93" t="s">
+        <v>79</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>29</v>
@@ -11575,13 +11022,13 @@
       <c r="BM81" s="4"/>
       <c r="BN81" s="4"/>
     </row>
-    <row r="82" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="82" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A82" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.6</v>
       </c>
-      <c r="B82" s="105" t="s">
-        <v>84</v>
+      <c r="B82" s="93" t="s">
+        <v>80</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>20</v>
@@ -11662,13 +11109,13 @@
       <c r="BM82" s="4"/>
       <c r="BN82" s="4"/>
     </row>
-    <row r="83" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="83" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A83" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.7</v>
       </c>
-      <c r="B83" s="105" t="s">
-        <v>85</v>
+      <c r="B83" s="93" t="s">
+        <v>81</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>29</v>
@@ -11749,16 +11196,16 @@
       <c r="BM83" s="4"/>
       <c r="BN83" s="4"/>
     </row>
-    <row r="84" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="84" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A84" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.8</v>
       </c>
-      <c r="B84" s="105" t="s">
-        <v>86</v>
+      <c r="B84" s="93" t="s">
+        <v>82</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D84" s="5"/>
       <c r="E84" s="6">
@@ -11836,13 +11283,13 @@
       <c r="BM84" s="4"/>
       <c r="BN84" s="4"/>
     </row>
-    <row r="85" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="85" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A85" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.9</v>
       </c>
-      <c r="B85" s="105" t="s">
-        <v>88</v>
+      <c r="B85" s="93" t="s">
+        <v>84</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>20</v>
@@ -11923,13 +11370,13 @@
       <c r="BM85" s="4"/>
       <c r="BN85" s="4"/>
     </row>
-    <row r="86" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="86" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A86" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.10</v>
       </c>
-      <c r="B86" s="105" t="s">
-        <v>89</v>
+      <c r="B86" s="93" t="s">
+        <v>85</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>29</v>
@@ -12010,13 +11457,13 @@
       <c r="BM86" s="4"/>
       <c r="BN86" s="4"/>
     </row>
-    <row r="87" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="87" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A87" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.11</v>
       </c>
-      <c r="B87" s="105" t="s">
-        <v>90</v>
+      <c r="B87" s="93" t="s">
+        <v>86</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>29</v>
@@ -12097,13 +11544,13 @@
       <c r="BM87" s="4"/>
       <c r="BN87" s="4"/>
     </row>
-    <row r="88" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="88" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A88" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.12</v>
       </c>
-      <c r="B88" s="105" t="s">
-        <v>91</v>
+      <c r="B88" s="93" t="s">
+        <v>87</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>20</v>
@@ -12184,13 +11631,13 @@
       <c r="BM88" s="4"/>
       <c r="BN88" s="4"/>
     </row>
-    <row r="89" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="89" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A89" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.13</v>
       </c>
-      <c r="B89" s="105" t="s">
-        <v>92</v>
+      <c r="B89" s="93" t="s">
+        <v>88</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>29</v>
@@ -12271,13 +11718,13 @@
       <c r="BM89" s="4"/>
       <c r="BN89" s="4"/>
     </row>
-    <row r="90" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="90" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A90" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.14</v>
       </c>
-      <c r="B90" s="105" t="s">
-        <v>93</v>
+      <c r="B90" s="93" t="s">
+        <v>89</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>29</v>
@@ -12358,13 +11805,13 @@
       <c r="BM90" s="4"/>
       <c r="BN90" s="4"/>
     </row>
-    <row r="91" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="91" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A91" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.15</v>
       </c>
-      <c r="B91" s="105" t="s">
-        <v>94</v>
+      <c r="B91" s="93" t="s">
+        <v>90</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>29</v>
@@ -12445,13 +11892,13 @@
       <c r="BM91" s="4"/>
       <c r="BN91" s="4"/>
     </row>
-    <row r="92" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="92" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A92" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.16</v>
       </c>
-      <c r="B92" s="105" t="s">
-        <v>95</v>
+      <c r="B92" s="93" t="s">
+        <v>91</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>29</v>
@@ -12532,13 +11979,13 @@
       <c r="BM92" s="4"/>
       <c r="BN92" s="4"/>
     </row>
-    <row r="93" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="93" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A93" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.17</v>
       </c>
-      <c r="B93" s="105" t="s">
-        <v>96</v>
+      <c r="B93" s="93" t="s">
+        <v>92</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>20</v>
@@ -12619,13 +12066,13 @@
       <c r="BM93" s="4"/>
       <c r="BN93" s="4"/>
     </row>
-    <row r="94" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="94" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A94" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.18</v>
       </c>
-      <c r="B94" s="105" t="s">
-        <v>97</v>
+      <c r="B94" s="93" t="s">
+        <v>93</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>29</v>
@@ -12706,13 +12153,13 @@
       <c r="BM94" s="4"/>
       <c r="BN94" s="4"/>
     </row>
-    <row r="95" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="95" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A95" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.19</v>
       </c>
-      <c r="B95" s="105" t="s">
-        <v>98</v>
+      <c r="B95" s="93" t="s">
+        <v>94</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>20</v>
@@ -12793,13 +12240,13 @@
       <c r="BM95" s="4"/>
       <c r="BN95" s="4"/>
     </row>
-    <row r="96" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="96" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A96" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.20</v>
       </c>
-      <c r="B96" s="105" t="s">
-        <v>99</v>
+      <c r="B96" s="93" t="s">
+        <v>95</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>29</v>
@@ -12880,13 +12327,13 @@
       <c r="BM96" s="4"/>
       <c r="BN96" s="4"/>
     </row>
-    <row r="97" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="97" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A97" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.21</v>
       </c>
-      <c r="B97" s="105" t="s">
-        <v>100</v>
+      <c r="B97" s="93" t="s">
+        <v>96</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>20</v>
@@ -12967,13 +12414,13 @@
       <c r="BM97" s="4"/>
       <c r="BN97" s="4"/>
     </row>
-    <row r="98" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="98" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A98" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.22</v>
       </c>
-      <c r="B98" s="105" t="s">
-        <v>101</v>
+      <c r="B98" s="93" t="s">
+        <v>97</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>29</v>
@@ -13054,13 +12501,13 @@
       <c r="BM98" s="4"/>
       <c r="BN98" s="4"/>
     </row>
-    <row r="99" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="99" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A99" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.23</v>
       </c>
-      <c r="B99" s="105" t="s">
-        <v>102</v>
+      <c r="B99" s="93" t="s">
+        <v>98</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>20</v>
@@ -13141,13 +12588,13 @@
       <c r="BM99" s="4"/>
       <c r="BN99" s="4"/>
     </row>
-    <row r="100" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="100" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A100" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.24</v>
       </c>
-      <c r="B100" s="105" t="s">
-        <v>103</v>
+      <c r="B100" s="93" t="s">
+        <v>99</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>29</v>
@@ -13228,13 +12675,13 @@
       <c r="BM100" s="4"/>
       <c r="BN100" s="4"/>
     </row>
-    <row r="101" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="101" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A101" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.25</v>
       </c>
-      <c r="B101" s="105" t="s">
-        <v>104</v>
+      <c r="B101" s="93" t="s">
+        <v>100</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>29</v>
@@ -13315,13 +12762,13 @@
       <c r="BM101" s="4"/>
       <c r="BN101" s="4"/>
     </row>
-    <row r="102" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="102" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A102" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.26</v>
       </c>
-      <c r="B102" s="105" t="s">
-        <v>105</v>
+      <c r="B102" s="93" t="s">
+        <v>101</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>29</v>
@@ -13402,13 +12849,13 @@
       <c r="BM102" s="4"/>
       <c r="BN102" s="4"/>
     </row>
-    <row r="103" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="103" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A103" s="4" t="str">
         <f t="shared" si="40"/>
         <v>1.27</v>
       </c>
-      <c r="B103" s="105" t="s">
-        <v>106</v>
+      <c r="B103" s="93" t="s">
+        <v>102</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>29</v>
@@ -13489,94 +12936,94 @@
       <c r="BM103" s="4"/>
       <c r="BN103" s="4"/>
     </row>
-    <row r="104" s="58" customFormat="1" ht="18" hidden="1" spans="1:66">
-      <c r="A104" s="112" t="str">
+    <row r="104" spans="1:66" s="55" customFormat="1" ht="18" hidden="1">
+      <c r="A104" s="100" t="str">
         <f>IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),TEXT(VALUE(prevWBS)+1,"#"),TEXT(VALUE(LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1))+1,"#")))</f>
         <v>2</v>
       </c>
-      <c r="B104" s="113" t="s">
-        <v>107</v>
-      </c>
-      <c r="D104" s="114"/>
-      <c r="E104" s="115"/>
-      <c r="F104" s="115" t="str">
+      <c r="B104" s="101" t="s">
+        <v>103</v>
+      </c>
+      <c r="D104" s="102"/>
+      <c r="E104" s="103"/>
+      <c r="F104" s="103" t="str">
         <f t="shared" si="47"/>
-        <v> - </v>
-      </c>
-      <c r="G104" s="116"/>
-      <c r="H104" s="117"/>
-      <c r="I104" s="118" t="str">
+        <v>-</v>
+      </c>
+      <c r="G104" s="104"/>
+      <c r="H104" s="105"/>
+      <c r="I104" s="106" t="str">
         <f t="shared" si="48"/>
-        <v> - </v>
-      </c>
-      <c r="J104" s="119"/>
-      <c r="K104" s="120"/>
-      <c r="L104" s="120"/>
-      <c r="M104" s="120"/>
-      <c r="N104" s="120"/>
-      <c r="O104" s="120"/>
-      <c r="P104" s="120"/>
-      <c r="Q104" s="120"/>
-      <c r="R104" s="120"/>
-      <c r="S104" s="120"/>
-      <c r="T104" s="120"/>
-      <c r="U104" s="120"/>
-      <c r="V104" s="120"/>
-      <c r="W104" s="120"/>
-      <c r="X104" s="120"/>
-      <c r="Y104" s="120"/>
-      <c r="Z104" s="120"/>
-      <c r="AA104" s="120"/>
-      <c r="AB104" s="120"/>
-      <c r="AC104" s="120"/>
-      <c r="AD104" s="120"/>
-      <c r="AE104" s="120"/>
-      <c r="AF104" s="120"/>
-      <c r="AG104" s="120"/>
-      <c r="AH104" s="120"/>
-      <c r="AI104" s="120"/>
-      <c r="AJ104" s="120"/>
-      <c r="AK104" s="120"/>
-      <c r="AL104" s="120"/>
-      <c r="AM104" s="120"/>
-      <c r="AN104" s="120"/>
-      <c r="AO104" s="120"/>
-      <c r="AP104" s="120"/>
-      <c r="AQ104" s="120"/>
-      <c r="AR104" s="120"/>
-      <c r="AS104" s="120"/>
-      <c r="AT104" s="120"/>
-      <c r="AU104" s="120"/>
-      <c r="AV104" s="120"/>
-      <c r="AW104" s="120"/>
-      <c r="AX104" s="120"/>
-      <c r="AY104" s="120"/>
-      <c r="AZ104" s="120"/>
-      <c r="BA104" s="120"/>
-      <c r="BB104" s="120"/>
-      <c r="BC104" s="120"/>
-      <c r="BD104" s="120"/>
-      <c r="BE104" s="120"/>
-      <c r="BF104" s="120"/>
-      <c r="BG104" s="120"/>
-      <c r="BH104" s="120"/>
-      <c r="BI104" s="120"/>
-      <c r="BJ104" s="120"/>
-      <c r="BK104" s="120"/>
-      <c r="BL104" s="120"/>
-      <c r="BM104" s="120"/>
-      <c r="BN104" s="120"/>
-    </row>
-    <row r="105" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+        <v>-</v>
+      </c>
+      <c r="J104" s="107"/>
+      <c r="K104" s="108"/>
+      <c r="L104" s="108"/>
+      <c r="M104" s="108"/>
+      <c r="N104" s="108"/>
+      <c r="O104" s="108"/>
+      <c r="P104" s="108"/>
+      <c r="Q104" s="108"/>
+      <c r="R104" s="108"/>
+      <c r="S104" s="108"/>
+      <c r="T104" s="108"/>
+      <c r="U104" s="108"/>
+      <c r="V104" s="108"/>
+      <c r="W104" s="108"/>
+      <c r="X104" s="108"/>
+      <c r="Y104" s="108"/>
+      <c r="Z104" s="108"/>
+      <c r="AA104" s="108"/>
+      <c r="AB104" s="108"/>
+      <c r="AC104" s="108"/>
+      <c r="AD104" s="108"/>
+      <c r="AE104" s="108"/>
+      <c r="AF104" s="108"/>
+      <c r="AG104" s="108"/>
+      <c r="AH104" s="108"/>
+      <c r="AI104" s="108"/>
+      <c r="AJ104" s="108"/>
+      <c r="AK104" s="108"/>
+      <c r="AL104" s="108"/>
+      <c r="AM104" s="108"/>
+      <c r="AN104" s="108"/>
+      <c r="AO104" s="108"/>
+      <c r="AP104" s="108"/>
+      <c r="AQ104" s="108"/>
+      <c r="AR104" s="108"/>
+      <c r="AS104" s="108"/>
+      <c r="AT104" s="108"/>
+      <c r="AU104" s="108"/>
+      <c r="AV104" s="108"/>
+      <c r="AW104" s="108"/>
+      <c r="AX104" s="108"/>
+      <c r="AY104" s="108"/>
+      <c r="AZ104" s="108"/>
+      <c r="BA104" s="108"/>
+      <c r="BB104" s="108"/>
+      <c r="BC104" s="108"/>
+      <c r="BD104" s="108"/>
+      <c r="BE104" s="108"/>
+      <c r="BF104" s="108"/>
+      <c r="BG104" s="108"/>
+      <c r="BH104" s="108"/>
+      <c r="BI104" s="108"/>
+      <c r="BJ104" s="108"/>
+      <c r="BK104" s="108"/>
+      <c r="BL104" s="108"/>
+      <c r="BM104" s="108"/>
+      <c r="BN104" s="108"/>
+    </row>
+    <row r="105" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A105" s="4" t="str">
         <f t="shared" si="40"/>
         <v>2.1</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D105" s="5"/>
       <c r="E105" s="6">
@@ -13654,16 +13101,16 @@
       <c r="BM105" s="4"/>
       <c r="BN105" s="4"/>
     </row>
-    <row r="106" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="106" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A106" s="4" t="str">
         <f t="shared" si="40"/>
         <v>2.2</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D106" s="5"/>
       <c r="E106" s="6">
@@ -13740,16 +13187,16 @@
       <c r="BM106" s="4"/>
       <c r="BN106" s="4"/>
     </row>
-    <row r="107" s="1" customFormat="1" ht="45" hidden="1" customHeight="1" spans="1:66">
+    <row r="107" spans="1:66" s="1" customFormat="1" ht="45" hidden="1" customHeight="1">
       <c r="A107" s="4" t="str">
         <f t="shared" si="40"/>
         <v>2.3</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D107" s="5"/>
       <c r="E107" s="6">
@@ -13826,94 +13273,94 @@
       <c r="BM107" s="4"/>
       <c r="BN107" s="4"/>
     </row>
-    <row r="108" s="58" customFormat="1" ht="18" hidden="1" spans="1:66">
-      <c r="A108" s="112" t="str">
+    <row r="108" spans="1:66" s="55" customFormat="1" ht="18" hidden="1">
+      <c r="A108" s="100" t="str">
         <f>IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),TEXT(VALUE(prevWBS)+1,"#"),TEXT(VALUE(LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1))+1,"#")))</f>
         <v>3</v>
       </c>
-      <c r="B108" s="113" t="s">
-        <v>112</v>
-      </c>
-      <c r="D108" s="114"/>
-      <c r="E108" s="115"/>
-      <c r="F108" s="115" t="str">
+      <c r="B108" s="101" t="s">
+        <v>108</v>
+      </c>
+      <c r="D108" s="102"/>
+      <c r="E108" s="103"/>
+      <c r="F108" s="103" t="str">
         <f t="shared" ref="F108:F113" si="53">IF(ISBLANK(E108)," - ",IF(G108=0,E108,E108+G108-1))</f>
-        <v> - </v>
-      </c>
-      <c r="G108" s="116"/>
-      <c r="H108" s="117"/>
-      <c r="I108" s="118" t="str">
+        <v>-</v>
+      </c>
+      <c r="G108" s="104"/>
+      <c r="H108" s="105"/>
+      <c r="I108" s="106" t="str">
         <f t="shared" ref="I108" si="54">IF(OR(F108=0,E108=0)," - ",NETWORKDAYS(E108,F108))</f>
-        <v> - </v>
-      </c>
-      <c r="J108" s="119"/>
-      <c r="K108" s="120"/>
-      <c r="L108" s="120"/>
-      <c r="M108" s="120"/>
-      <c r="N108" s="120"/>
-      <c r="O108" s="120"/>
-      <c r="P108" s="120"/>
-      <c r="Q108" s="120"/>
-      <c r="R108" s="120"/>
-      <c r="S108" s="120"/>
-      <c r="T108" s="120"/>
-      <c r="U108" s="120"/>
-      <c r="V108" s="120"/>
-      <c r="W108" s="120"/>
-      <c r="X108" s="120"/>
-      <c r="Y108" s="120"/>
-      <c r="Z108" s="120"/>
-      <c r="AA108" s="120"/>
-      <c r="AB108" s="120"/>
-      <c r="AC108" s="120"/>
-      <c r="AD108" s="120"/>
-      <c r="AE108" s="120"/>
-      <c r="AF108" s="120"/>
-      <c r="AG108" s="120"/>
-      <c r="AH108" s="120"/>
-      <c r="AI108" s="120"/>
-      <c r="AJ108" s="120"/>
-      <c r="AK108" s="120"/>
-      <c r="AL108" s="120"/>
-      <c r="AM108" s="120"/>
-      <c r="AN108" s="120"/>
-      <c r="AO108" s="120"/>
-      <c r="AP108" s="120"/>
-      <c r="AQ108" s="120"/>
-      <c r="AR108" s="120"/>
-      <c r="AS108" s="120"/>
-      <c r="AT108" s="120"/>
-      <c r="AU108" s="120"/>
-      <c r="AV108" s="120"/>
-      <c r="AW108" s="120"/>
-      <c r="AX108" s="120"/>
-      <c r="AY108" s="120"/>
-      <c r="AZ108" s="120"/>
-      <c r="BA108" s="120"/>
-      <c r="BB108" s="120"/>
-      <c r="BC108" s="120"/>
-      <c r="BD108" s="120"/>
-      <c r="BE108" s="120"/>
-      <c r="BF108" s="120"/>
-      <c r="BG108" s="120"/>
-      <c r="BH108" s="120"/>
-      <c r="BI108" s="120"/>
-      <c r="BJ108" s="120"/>
-      <c r="BK108" s="120"/>
-      <c r="BL108" s="120"/>
-      <c r="BM108" s="120"/>
-      <c r="BN108" s="120"/>
-    </row>
-    <row r="109" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+        <v>-</v>
+      </c>
+      <c r="J108" s="107"/>
+      <c r="K108" s="108"/>
+      <c r="L108" s="108"/>
+      <c r="M108" s="108"/>
+      <c r="N108" s="108"/>
+      <c r="O108" s="108"/>
+      <c r="P108" s="108"/>
+      <c r="Q108" s="108"/>
+      <c r="R108" s="108"/>
+      <c r="S108" s="108"/>
+      <c r="T108" s="108"/>
+      <c r="U108" s="108"/>
+      <c r="V108" s="108"/>
+      <c r="W108" s="108"/>
+      <c r="X108" s="108"/>
+      <c r="Y108" s="108"/>
+      <c r="Z108" s="108"/>
+      <c r="AA108" s="108"/>
+      <c r="AB108" s="108"/>
+      <c r="AC108" s="108"/>
+      <c r="AD108" s="108"/>
+      <c r="AE108" s="108"/>
+      <c r="AF108" s="108"/>
+      <c r="AG108" s="108"/>
+      <c r="AH108" s="108"/>
+      <c r="AI108" s="108"/>
+      <c r="AJ108" s="108"/>
+      <c r="AK108" s="108"/>
+      <c r="AL108" s="108"/>
+      <c r="AM108" s="108"/>
+      <c r="AN108" s="108"/>
+      <c r="AO108" s="108"/>
+      <c r="AP108" s="108"/>
+      <c r="AQ108" s="108"/>
+      <c r="AR108" s="108"/>
+      <c r="AS108" s="108"/>
+      <c r="AT108" s="108"/>
+      <c r="AU108" s="108"/>
+      <c r="AV108" s="108"/>
+      <c r="AW108" s="108"/>
+      <c r="AX108" s="108"/>
+      <c r="AY108" s="108"/>
+      <c r="AZ108" s="108"/>
+      <c r="BA108" s="108"/>
+      <c r="BB108" s="108"/>
+      <c r="BC108" s="108"/>
+      <c r="BD108" s="108"/>
+      <c r="BE108" s="108"/>
+      <c r="BF108" s="108"/>
+      <c r="BG108" s="108"/>
+      <c r="BH108" s="108"/>
+      <c r="BI108" s="108"/>
+      <c r="BJ108" s="108"/>
+      <c r="BK108" s="108"/>
+      <c r="BL108" s="108"/>
+      <c r="BM108" s="108"/>
+      <c r="BN108" s="108"/>
+    </row>
+    <row r="109" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A109" s="4" t="str">
         <f t="shared" si="40"/>
         <v>3.1</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D109" s="5"/>
       <c r="E109" s="6">
@@ -13990,16 +13437,16 @@
       <c r="BM109" s="4"/>
       <c r="BN109" s="4"/>
     </row>
-    <row r="110" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="110" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A110" s="4" t="str">
         <f t="shared" si="40"/>
         <v>3.2</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D110" s="5"/>
       <c r="E110" s="6">
@@ -14076,13 +13523,13 @@
       <c r="BM110" s="4"/>
       <c r="BN110" s="4"/>
     </row>
-    <row r="111" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="111" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A111" s="4" t="str">
         <f t="shared" si="40"/>
         <v>3.3</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>20</v>
@@ -14162,13 +13609,13 @@
       <c r="BM111" s="4"/>
       <c r="BN111" s="4"/>
     </row>
-    <row r="112" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="112" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A112" s="4" t="str">
         <f t="shared" si="40"/>
         <v>3.4</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>20</v>
@@ -14248,13 +13695,13 @@
       <c r="BM112" s="4"/>
       <c r="BN112" s="4"/>
     </row>
-    <row r="113" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+    <row r="113" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A113" s="4" t="str">
         <f t="shared" si="40"/>
         <v>3.5</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>29</v>
@@ -14334,94 +13781,94 @@
       <c r="BM113" s="4"/>
       <c r="BN113" s="4"/>
     </row>
-    <row r="114" s="58" customFormat="1" ht="18" hidden="1" spans="1:66">
-      <c r="A114" s="112" t="str">
+    <row r="114" spans="1:66" s="55" customFormat="1" ht="18" hidden="1">
+      <c r="A114" s="100" t="str">
         <f>IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),TEXT(VALUE(prevWBS)+1,"#"),TEXT(VALUE(LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1))+1,"#")))</f>
         <v>4</v>
       </c>
-      <c r="B114" s="113" t="s">
-        <v>118</v>
-      </c>
-      <c r="D114" s="114"/>
-      <c r="E114" s="115"/>
-      <c r="F114" s="115" t="str">
+      <c r="B114" s="101" t="s">
+        <v>114</v>
+      </c>
+      <c r="D114" s="102"/>
+      <c r="E114" s="103"/>
+      <c r="F114" s="103" t="str">
         <f t="shared" ref="F114:F115" si="55">IF(ISBLANK(E114)," - ",IF(G114=0,E114,E114+G114-1))</f>
-        <v> - </v>
-      </c>
-      <c r="G114" s="116"/>
-      <c r="H114" s="117"/>
-      <c r="I114" s="118" t="str">
+        <v>-</v>
+      </c>
+      <c r="G114" s="104"/>
+      <c r="H114" s="105"/>
+      <c r="I114" s="106" t="str">
         <f t="shared" ref="I114" si="56">IF(OR(F114=0,E114=0)," - ",NETWORKDAYS(E114,F114))</f>
-        <v> - </v>
-      </c>
-      <c r="J114" s="119"/>
-      <c r="K114" s="120"/>
-      <c r="L114" s="120"/>
-      <c r="M114" s="120"/>
-      <c r="N114" s="120"/>
-      <c r="O114" s="120"/>
-      <c r="P114" s="120"/>
-      <c r="Q114" s="120"/>
-      <c r="R114" s="120"/>
-      <c r="S114" s="120"/>
-      <c r="T114" s="120"/>
-      <c r="U114" s="120"/>
-      <c r="V114" s="120"/>
-      <c r="W114" s="120"/>
-      <c r="X114" s="120"/>
-      <c r="Y114" s="120"/>
-      <c r="Z114" s="120"/>
-      <c r="AA114" s="120"/>
-      <c r="AB114" s="120"/>
-      <c r="AC114" s="120"/>
-      <c r="AD114" s="120"/>
-      <c r="AE114" s="120"/>
-      <c r="AF114" s="120"/>
-      <c r="AG114" s="120"/>
-      <c r="AH114" s="120"/>
-      <c r="AI114" s="120"/>
-      <c r="AJ114" s="120"/>
-      <c r="AK114" s="120"/>
-      <c r="AL114" s="120"/>
-      <c r="AM114" s="120"/>
-      <c r="AN114" s="120"/>
-      <c r="AO114" s="120"/>
-      <c r="AP114" s="120"/>
-      <c r="AQ114" s="120"/>
-      <c r="AR114" s="120"/>
-      <c r="AS114" s="120"/>
-      <c r="AT114" s="120"/>
-      <c r="AU114" s="120"/>
-      <c r="AV114" s="120"/>
-      <c r="AW114" s="120"/>
-      <c r="AX114" s="120"/>
-      <c r="AY114" s="120"/>
-      <c r="AZ114" s="120"/>
-      <c r="BA114" s="120"/>
-      <c r="BB114" s="120"/>
-      <c r="BC114" s="120"/>
-      <c r="BD114" s="120"/>
-      <c r="BE114" s="120"/>
-      <c r="BF114" s="120"/>
-      <c r="BG114" s="120"/>
-      <c r="BH114" s="120"/>
-      <c r="BI114" s="120"/>
-      <c r="BJ114" s="120"/>
-      <c r="BK114" s="120"/>
-      <c r="BL114" s="120"/>
-      <c r="BM114" s="120"/>
-      <c r="BN114" s="120"/>
-    </row>
-    <row r="115" s="1" customFormat="1" ht="18" hidden="1" spans="1:66">
+        <v>-</v>
+      </c>
+      <c r="J114" s="107"/>
+      <c r="K114" s="108"/>
+      <c r="L114" s="108"/>
+      <c r="M114" s="108"/>
+      <c r="N114" s="108"/>
+      <c r="O114" s="108"/>
+      <c r="P114" s="108"/>
+      <c r="Q114" s="108"/>
+      <c r="R114" s="108"/>
+      <c r="S114" s="108"/>
+      <c r="T114" s="108"/>
+      <c r="U114" s="108"/>
+      <c r="V114" s="108"/>
+      <c r="W114" s="108"/>
+      <c r="X114" s="108"/>
+      <c r="Y114" s="108"/>
+      <c r="Z114" s="108"/>
+      <c r="AA114" s="108"/>
+      <c r="AB114" s="108"/>
+      <c r="AC114" s="108"/>
+      <c r="AD114" s="108"/>
+      <c r="AE114" s="108"/>
+      <c r="AF114" s="108"/>
+      <c r="AG114" s="108"/>
+      <c r="AH114" s="108"/>
+      <c r="AI114" s="108"/>
+      <c r="AJ114" s="108"/>
+      <c r="AK114" s="108"/>
+      <c r="AL114" s="108"/>
+      <c r="AM114" s="108"/>
+      <c r="AN114" s="108"/>
+      <c r="AO114" s="108"/>
+      <c r="AP114" s="108"/>
+      <c r="AQ114" s="108"/>
+      <c r="AR114" s="108"/>
+      <c r="AS114" s="108"/>
+      <c r="AT114" s="108"/>
+      <c r="AU114" s="108"/>
+      <c r="AV114" s="108"/>
+      <c r="AW114" s="108"/>
+      <c r="AX114" s="108"/>
+      <c r="AY114" s="108"/>
+      <c r="AZ114" s="108"/>
+      <c r="BA114" s="108"/>
+      <c r="BB114" s="108"/>
+      <c r="BC114" s="108"/>
+      <c r="BD114" s="108"/>
+      <c r="BE114" s="108"/>
+      <c r="BF114" s="108"/>
+      <c r="BG114" s="108"/>
+      <c r="BH114" s="108"/>
+      <c r="BI114" s="108"/>
+      <c r="BJ114" s="108"/>
+      <c r="BK114" s="108"/>
+      <c r="BL114" s="108"/>
+      <c r="BM114" s="108"/>
+      <c r="BN114" s="108"/>
+    </row>
+    <row r="115" spans="1:66" s="1" customFormat="1" ht="18" hidden="1">
       <c r="A115" s="4" t="str">
         <f t="shared" si="40"/>
         <v>4.1</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D115" s="5"/>
       <c r="E115" s="6">
@@ -14501,36 +13948,36 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0"/>
   <mergeCells count="19">
+    <mergeCell ref="AM5:AS5"/>
+    <mergeCell ref="AT5:AZ5"/>
+    <mergeCell ref="BA5:BG5"/>
+    <mergeCell ref="BH5:BN5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="R5:X5"/>
+    <mergeCell ref="Y5:AE5"/>
+    <mergeCell ref="AF5:AL5"/>
+    <mergeCell ref="AF4:AL4"/>
+    <mergeCell ref="AM4:AS4"/>
+    <mergeCell ref="AT4:AZ4"/>
+    <mergeCell ref="BA4:BG4"/>
+    <mergeCell ref="BH4:BN4"/>
     <mergeCell ref="K1:AE1"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="K4:Q4"/>
     <mergeCell ref="R4:X4"/>
     <mergeCell ref="Y4:AE4"/>
-    <mergeCell ref="AF4:AL4"/>
-    <mergeCell ref="AM4:AS4"/>
-    <mergeCell ref="AT4:AZ4"/>
-    <mergeCell ref="BA4:BG4"/>
-    <mergeCell ref="BH4:BN4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="K5:Q5"/>
-    <mergeCell ref="R5:X5"/>
-    <mergeCell ref="Y5:AE5"/>
-    <mergeCell ref="AF5:AL5"/>
-    <mergeCell ref="AM5:AS5"/>
-    <mergeCell ref="AT5:AZ5"/>
-    <mergeCell ref="BA5:BG5"/>
-    <mergeCell ref="BH5:BN5"/>
   </mergeCells>
   <conditionalFormatting sqref="H11">
     <cfRule type="dataBar" priority="157">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5d411fd4-3e54-4bd1-8532-6c23ebbd552e}</x14:id>
+          <x14:id>{5D411FD4-3E54-4BD1-8532-6C23EBBD552E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14540,11 +13987,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a496e16e-e84b-4e22-b781-7a016aac9a6d}</x14:id>
+          <x14:id>{A496E16E-E84B-4E22-B781-7A016AAC9A6D}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14554,11 +14001,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{77833048-568d-4394-81c6-5bd49732c40b}</x14:id>
+          <x14:id>{77833048-568D-4394-81C6-5BD49732C40B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14568,11 +14015,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{64de3f20-31b0-43d1-b0b2-3fa0fab992eb}</x14:id>
+          <x14:id>{64DE3F20-31B0-43D1-B0B2-3FA0FAB992EB}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14582,11 +14029,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3d7da7f9-34ef-413c-97fe-5c685264e782}</x14:id>
+          <x14:id>{3D7DA7F9-34EF-413C-97FE-5C685264E782}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14596,11 +14043,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2e4bee17-1ad8-4ee1-abfa-ce8dbb66f5b9}</x14:id>
+          <x14:id>{2E4BEE17-1AD8-4EE1-ABFA-CE8DBB66F5B9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14610,11 +14057,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c34c3a4a-b2f1-4a99-baad-377aa832d261}</x14:id>
+          <x14:id>{C34C3A4A-B2F1-4A99-BAAD-377AA832D261}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14624,11 +14071,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e5cc2ab0-9781-47a5-83e2-8bb2d8186002}</x14:id>
+          <x14:id>{E5CC2AB0-9781-47A5-83E2-8BB2D8186002}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14638,11 +14085,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ce678e65-4430-4631-8c47-0ff523236192}</x14:id>
+          <x14:id>{CE678E65-4430-4631-8C47-0FF523236192}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14652,11 +14099,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{51568b3e-4d28-4e71-862f-e0478db892d9}</x14:id>
+          <x14:id>{51568B3E-4D28-4E71-862F-E0478DB892D9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14666,11 +14113,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4c8ab46a-d580-445f-8550-ba3b7d59e2cc}</x14:id>
+          <x14:id>{4C8AB46A-D580-445F-8550-BA3B7D59E2CC}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14680,17 +14127,17 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d04ee583-134d-478e-8ab2-5c89c9f8da03}</x14:id>
+          <x14:id>{D04EE583-134D-478E-8AB2-5C89C9F8DA03}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K45:BN45">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>K$6=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14699,11 +14146,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3e29c452-c19c-45aa-819a-55686b848aa2}</x14:id>
+          <x14:id>{3E29C452-C19C-45AA-819A-55686B848AA2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14713,11 +14160,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{61761229-4066-4a43-abbe-c3c05d55411e}</x14:id>
+          <x14:id>{61761229-4066-4A43-ABBE-C3C05D55411E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14727,11 +14174,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4bd8555b-f8ef-4def-a90c-742d657b31b8}</x14:id>
+          <x14:id>{4BD8555B-F8EF-4DEF-A90C-742D657B31B8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14741,11 +14188,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{94d7114f-d901-499b-853b-a9d3f8d72229}</x14:id>
+          <x14:id>{94D7114F-D901-499B-853B-A9D3F8D72229}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14755,11 +14202,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{28fe73b8-970e-4b74-b1cc-3aa74da97c53}</x14:id>
+          <x14:id>{28FE73B8-970E-4B74-B1CC-3AA74DA97C53}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14769,11 +14216,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d563c6e6-3f8a-427e-9281-dcce7ba88388}</x14:id>
+          <x14:id>{D563C6E6-3F8A-427E-9281-DCCE7BA88388}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14783,11 +14230,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a26bcb48-3981-4275-86c9-8f9ccb05a23e}</x14:id>
+          <x14:id>{A26BCB48-3981-4275-86C9-8F9CCB05A23E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14797,11 +14244,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{86df5821-015a-4484-9b4f-444d478234bb}</x14:id>
+          <x14:id>{86DF5821-015A-4484-9B4F-444D478234BB}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14811,11 +14258,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b3794ffa-68f2-4e38-b13b-c3a74f4f71cf}</x14:id>
+          <x14:id>{B3794FFA-68F2-4E38-B13B-C3A74F4F71CF}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14825,11 +14272,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5f5c5c2f-c25c-4ed4-ba16-edd220e27648}</x14:id>
+          <x14:id>{5F5C5C2F-C25C-4ED4-BA16-EDD220E27648}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14839,11 +14286,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6523ba1b-cfc8-405a-93e8-d131011e3f73}</x14:id>
+          <x14:id>{6523BA1B-CFC8-405A-93E8-D131011E3F73}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14853,11 +14300,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2be7505a-dd50-49f2-a8b9-38edd684022b}</x14:id>
+          <x14:id>{2BE7505A-DD50-49F2-A8B9-38EDD684022B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14867,11 +14314,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{540e5c62-18e7-47a5-8a80-93b435cfd9e0}</x14:id>
+          <x14:id>{540E5C62-18E7-47A5-8A80-93B435CFD9E0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14881,11 +14328,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e87de01a-8f41-4462-af3b-619e8d6b67e5}</x14:id>
+          <x14:id>{E87DE01A-8F41-4462-AF3B-619E8D6B67E5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14895,11 +14342,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c078e29b-b0ea-4b50-b7f5-6a0a5cbdf788}</x14:id>
+          <x14:id>{C078E29B-B0EA-4B50-B7F5-6A0A5CBDF788}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14909,11 +14356,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec64beee-3e2c-4ed8-8c0a-82e233a8b6f3}</x14:id>
+          <x14:id>{EC64BEEE-3E2C-4ED8-8C0A-82E233A8B6F3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14923,11 +14370,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{11425af0-9cfc-42b8-84a7-dfbe45c809e7}</x14:id>
+          <x14:id>{11425AF0-9CFC-42B8-84A7-DFBE45C809E7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14937,11 +14384,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{52af7a61-f799-44f9-a1ae-629f62f1e696}</x14:id>
+          <x14:id>{52AF7A61-F799-44F9-A1AE-629F62F1E696}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14951,22 +14398,22 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{01264bb0-cdea-485a-80e2-0525f0f2c226}</x14:id>
+          <x14:id>{01264BB0-CDEA-485A-80E2-0525F0F2C226}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:BN7">
-    <cfRule type="expression" dxfId="1" priority="313">
+    <cfRule type="expression" dxfId="9" priority="313">
       <formula>K$6=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:BN44 K46:BN60">
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="8" priority="5">
       <formula>K$6=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14975,20 +14422,20 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5629a077-ac46-4b24-a4fe-aa98ef2453d7}</x14:id>
+          <x14:id>{5629A077-AC46-4B24-A4FE-AA98EF2453D7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8:BN60">
-    <cfRule type="expression" dxfId="2" priority="6">
+    <cfRule type="expression" dxfId="7" priority="6">
       <formula>AND($E8&lt;=K$6,ROUNDDOWN(($F8-$E8+1)*$H8,0)+$E8-1&gt;=K$6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="7">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>AND(NOT(ISBLANK($E8)),$E8&lt;=K$6,$F8&gt;=K$6)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14997,20 +14444,20 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{03f1b327-66b8-4a98-9ee4-a8ffa1ee7d03}</x14:id>
+          <x14:id>{03F1B327-66B8-4A98-9EE4-A8FFA1EE7D03}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K62:BN115">
-    <cfRule type="expression" dxfId="0" priority="98">
+    <cfRule type="expression" dxfId="5" priority="98">
       <formula>K$6=TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="99">
+    <cfRule type="expression" dxfId="4" priority="99">
       <formula>AND($E62&lt;=K$6,ROUNDDOWN(($F62-$E62+1)*$H62,0)+$E62-1&gt;=K$6)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="100">
@@ -15021,21 +14468,21 @@
     <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Display Week" prompt="Enter the week number to display first in the Gantt Chart. The weeks are numbered starting from the week containing the Project Start Date." sqref="H4"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.25"/>
-  <pageSetup paperSize="1" scale="53" orientation="landscape"/>
+  <pageSetup scale="53" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
   <ignoredErrors>
     <ignoredError sqref="A76" formula="1"/>
     <ignoredError sqref="H78:H80 G76:H76 E76" unlockedFormula="1"/>
   </ignoredErrors>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="8238" name="Scroll Bar 46" r:id="rId4">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="8238" r:id="rId3" name="Scroll Bar 46">
+              <controlPr defaultSize="0" print="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>9</xdr:col>
@@ -15061,7 +14508,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5d411fd4-3e54-4bd1-8532-6c23ebbd552e}">
+          <x14:cfRule type="dataBar" id="{5D411FD4-3E54-4BD1-8532-6C23EBBD552E}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15076,7 +14523,7 @@
           <xm:sqref>H11</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a496e16e-e84b-4e22-b781-7a016aac9a6d}">
+          <x14:cfRule type="dataBar" id="{A496E16E-E84B-4E22-B781-7A016AAC9A6D}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15091,7 +14538,7 @@
           <xm:sqref>H18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{77833048-568d-4394-81c6-5bd49732c40b}">
+          <x14:cfRule type="dataBar" id="{77833048-568D-4394-81C6-5BD49732C40B}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15106,7 +14553,7 @@
           <xm:sqref>H19</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{64de3f20-31b0-43d1-b0b2-3fa0fab992eb}">
+          <x14:cfRule type="dataBar" id="{64DE3F20-31B0-43D1-B0B2-3FA0FAB992EB}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15121,7 +14568,7 @@
           <xm:sqref>H32</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3d7da7f9-34ef-413c-97fe-5c685264e782}">
+          <x14:cfRule type="dataBar" id="{3D7DA7F9-34EF-413C-97FE-5C685264E782}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15136,7 +14583,7 @@
           <xm:sqref>H33</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2e4bee17-1ad8-4ee1-abfa-ce8dbb66f5b9}">
+          <x14:cfRule type="dataBar" id="{2E4BEE17-1AD8-4EE1-ABFA-CE8DBB66F5B9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15151,7 +14598,7 @@
           <xm:sqref>H34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c34c3a4a-b2f1-4a99-baad-377aa832d261}">
+          <x14:cfRule type="dataBar" id="{C34C3A4A-B2F1-4A99-BAAD-377AA832D261}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15166,7 +14613,7 @@
           <xm:sqref>H35</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e5cc2ab0-9781-47a5-83e2-8bb2d8186002}">
+          <x14:cfRule type="dataBar" id="{E5CC2AB0-9781-47A5-83E2-8BB2D8186002}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15181,7 +14628,7 @@
           <xm:sqref>H36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ce678e65-4430-4631-8c47-0ff523236192}">
+          <x14:cfRule type="dataBar" id="{CE678E65-4430-4631-8C47-0FF523236192}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15196,7 +14643,7 @@
           <xm:sqref>H37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{51568b3e-4d28-4e71-862f-e0478db892d9}">
+          <x14:cfRule type="dataBar" id="{51568B3E-4D28-4E71-862F-E0478DB892D9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15211,7 +14658,7 @@
           <xm:sqref>H38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4c8ab46a-d580-445f-8550-ba3b7d59e2cc}">
+          <x14:cfRule type="dataBar" id="{4C8AB46A-D580-445F-8550-BA3B7D59E2CC}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15226,7 +14673,7 @@
           <xm:sqref>H39</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d04ee583-134d-478e-8ab2-5c89c9f8da03}">
+          <x14:cfRule type="dataBar" id="{D04EE583-134D-478E-8AB2-5C89C9F8DA03}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15241,7 +14688,7 @@
           <xm:sqref>H45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3e29c452-c19c-45aa-819a-55686b848aa2}">
+          <x14:cfRule type="dataBar" id="{3E29C452-C19C-45AA-819A-55686B848AA2}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15256,7 +14703,7 @@
           <xm:sqref>H90</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{61761229-4066-4a43-abbe-c3c05d55411e}">
+          <x14:cfRule type="dataBar" id="{61761229-4066-4A43-ABBE-C3C05D55411E}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15271,7 +14718,7 @@
           <xm:sqref>H91</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4bd8555b-f8ef-4def-a90c-742d657b31b8}">
+          <x14:cfRule type="dataBar" id="{4BD8555B-F8EF-4DEF-A90C-742D657B31B8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15286,7 +14733,7 @@
           <xm:sqref>H99</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{94d7114f-d901-499b-853b-a9d3f8d72229}">
+          <x14:cfRule type="dataBar" id="{94D7114F-D901-499B-853B-A9D3F8D72229}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15301,7 +14748,7 @@
           <xm:sqref>H100</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{28fe73b8-970e-4b74-b1cc-3aa74da97c53}">
+          <x14:cfRule type="dataBar" id="{28FE73B8-970E-4B74-B1CC-3AA74DA97C53}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15316,7 +14763,7 @@
           <xm:sqref>H101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d563c6e6-3f8a-427e-9281-dcce7ba88388}">
+          <x14:cfRule type="dataBar" id="{D563C6E6-3F8A-427E-9281-DCCE7BA88388}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15331,7 +14778,7 @@
           <xm:sqref>H102</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a26bcb48-3981-4275-86c9-8f9ccb05a23e}">
+          <x14:cfRule type="dataBar" id="{A26BCB48-3981-4275-86C9-8F9CCB05A23E}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15346,7 +14793,7 @@
           <xm:sqref>H103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{86df5821-015a-4484-9b4f-444d478234bb}">
+          <x14:cfRule type="dataBar" id="{86DF5821-015A-4484-9B4F-444D478234BB}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15361,7 +14808,7 @@
           <xm:sqref>H104</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b3794ffa-68f2-4e38-b13b-c3a74f4f71cf}">
+          <x14:cfRule type="dataBar" id="{B3794FFA-68F2-4E38-B13B-C3A74F4F71CF}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15376,7 +14823,7 @@
           <xm:sqref>H108</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5f5c5c2f-c25c-4ed4-ba16-edd220e27648}">
+          <x14:cfRule type="dataBar" id="{5F5C5C2F-C25C-4ED4-BA16-EDD220E27648}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15391,7 +14838,7 @@
           <xm:sqref>H114</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6523ba1b-cfc8-405a-93e8-d131011e3f73}">
+          <x14:cfRule type="dataBar" id="{6523BA1B-CFC8-405A-93E8-D131011E3F73}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15406,7 +14853,7 @@
           <xm:sqref>H115</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2be7505a-dd50-49f2-a8b9-38edd684022b}">
+          <x14:cfRule type="dataBar" id="{2BE7505A-DD50-49F2-A8B9-38EDD684022B}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15421,7 +14868,7 @@
           <xm:sqref>H12:H15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{540e5c62-18e7-47a5-8a80-93b435cfd9e0}">
+          <x14:cfRule type="dataBar" id="{540E5C62-18E7-47A5-8A80-93B435CFD9E0}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15436,7 +14883,7 @@
           <xm:sqref>H16:H17</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e87de01a-8f41-4462-af3b-619e8d6b67e5}">
+          <x14:cfRule type="dataBar" id="{E87DE01A-8F41-4462-AF3B-619E8D6B67E5}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15451,7 +14898,7 @@
           <xm:sqref>H82:H86</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c078e29b-b0ea-4b50-b7f5-6a0a5cbdf788}">
+          <x14:cfRule type="dataBar" id="{C078E29B-B0EA-4B50-B7F5-6A0A5CBDF788}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15466,7 +14913,7 @@
           <xm:sqref>H87:H89</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ec64beee-3e2c-4ed8-8c0a-82e233a8b6f3}">
+          <x14:cfRule type="dataBar" id="{EC64BEEE-3E2C-4ED8-8C0A-82E233A8B6F3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15481,7 +14928,7 @@
           <xm:sqref>H92:H96</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{11425af0-9cfc-42b8-84a7-dfbe45c809e7}">
+          <x14:cfRule type="dataBar" id="{11425AF0-9CFC-42B8-84A7-DFBE45C809E7}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15496,7 +14943,7 @@
           <xm:sqref>H97:H98</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{52af7a61-f799-44f9-a1ae-629f62f1e696}">
+          <x14:cfRule type="dataBar" id="{52AF7A61-F799-44F9-A1AE-629F62F1E696}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15511,7 +14958,7 @@
           <xm:sqref>H105:H107</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{01264bb0-cdea-485a-80e2-0525f0f2c226}">
+          <x14:cfRule type="dataBar" id="{01264BB0-CDEA-485A-80E2-0525F0F2C226}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15526,7 +14973,7 @@
           <xm:sqref>H109:H113</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5629a077-ac46-4b24-a4fe-aa98ef2453d7}">
+          <x14:cfRule type="dataBar" id="{5629A077-AC46-4B24-A4FE-AA98EF2453D7}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15541,7 +14988,7 @@
           <xm:sqref>H8:H10 H76:H81 H20:H31</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{03f1b327-66b8-4a98-9ee4-a8ffa1ee7d03}">
+          <x14:cfRule type="dataBar" id="{03F1B327-66B8-4A98-9EE4-A8FFA1EE7D03}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -15562,921 +15009,918 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
-    <col min="2" max="2" width="37.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="55.1428571428571" customWidth="1"/>
-    <col min="4" max="7" width="8.85714285714286"/>
+    <col min="1" max="1" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="37.7109375" customWidth="1"/>
+    <col min="3" max="3" width="55.140625" customWidth="1"/>
+    <col min="4" max="7" width="8.85546875"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:3">
-      <c r="A1" s="54" t="s">
-        <v>120</v>
+    <row r="1" spans="1:3" ht="30" customHeight="1">
+      <c r="A1" s="51" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="C4" s="38" t="s">
-        <v>121</v>
+      <c r="C4" s="36" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="C5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" ht="18" spans="1:3">
-      <c r="C7" s="55" t="s">
-        <v>123</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18">
+      <c r="C7" s="52" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="C8" s="56" t="s">
-        <v>124</v>
+      <c r="C8" s="53" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="C10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="C11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="13" ht="18" spans="1:3">
-      <c r="C13" s="55" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" spans="1:3">
-      <c r="A16" s="28" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="18" ht="15" spans="2:2">
-      <c r="B18" s="57" t="s">
-        <v>129</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18">
+      <c r="C13" s="52" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75">
+      <c r="A16" s="27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" ht="15">
+      <c r="B18" s="54" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="2:2">
-      <c r="B22" s="57" t="s">
-        <v>132</v>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" ht="15">
+      <c r="B22" s="54" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="26" ht="15" spans="2:2">
-      <c r="B26" s="57" t="s">
-        <v>135</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" ht="15">
+      <c r="B26" s="54" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="34" ht="15" spans="2:2">
-      <c r="B34" s="57" t="s">
-        <v>142</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" ht="15">
+      <c r="B34" s="54" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="39" ht="15" spans="2:2">
-      <c r="B39" s="57" t="s">
-        <v>146</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" ht="15">
+      <c r="B39" s="54" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="42" ht="15" spans="2:2">
-      <c r="B42" s="57" t="s">
-        <v>148</v>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" ht="15">
+      <c r="B42" s="54" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="46" ht="18" spans="2:2">
-      <c r="B46" s="55" t="s">
-        <v>151</v>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" ht="18">
+      <c r="B46" s="52" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C7" r:id="rId2" display="Learn About Gantt Chart Template Pro"/>
-    <hyperlink ref="B46" r:id="rId2" display="Learn More About Gantt Chart Template Pro" tooltip="Go to Vertex42.com"/>
-    <hyperlink ref="C13" r:id="rId3" display="Gantt Chart Template Pro for Excel Online"/>
+    <hyperlink ref="C7" r:id="rId1"/>
+    <hyperlink ref="B46" r:id="rId2" tooltip="Go to Vertex42.com"/>
+    <hyperlink ref="C13" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" scale="93" orientation="portrait"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
+  <pageSetup scale="93" orientation="portrait"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C94"/>
-  <sheetFormatPr defaultColWidth="8.85714285714286" defaultRowHeight="12.75" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
-    <col min="2" max="2" width="90.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="16.4285714285714" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="90.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:3" ht="30" customHeight="1">
+      <c r="A1" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="23"/>
+    </row>
+    <row r="2" spans="1:3" ht="14.25">
+      <c r="A2" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="25"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="B3" s="25"/>
+    </row>
+    <row r="4" spans="1:3" ht="18">
+      <c r="A4" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="27"/>
+    </row>
+    <row r="5" spans="1:3" ht="57">
+      <c r="B5" s="28" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="28.5">
+      <c r="B7" s="28" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="14.25">
+      <c r="B9" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="24"/>
-    </row>
-    <row r="2" ht="14.25" spans="1:3">
-      <c r="A2" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="B2" s="26"/>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="B3" s="26"/>
-    </row>
-    <row r="4" ht="18" spans="1:3">
-      <c r="A4" s="27" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="28.5">
+      <c r="B11" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="28"/>
-    </row>
-    <row r="5" ht="57" spans="1:3">
-      <c r="B5" s="29" t="s">
+    </row>
+    <row r="13" spans="1:3" ht="18">
+      <c r="A13" s="120" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="7" ht="28.5" spans="1:3">
-      <c r="B7" s="29" t="s">
+      <c r="B13" s="120"/>
+    </row>
+    <row r="15" spans="1:3" s="22" customFormat="1" ht="18">
+      <c r="A15" s="30"/>
+      <c r="B15" s="31" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="1:3">
-      <c r="B9" s="25" t="s">
+    <row r="16" spans="1:3" s="22" customFormat="1" ht="18">
+      <c r="A16" s="30"/>
+      <c r="B16" s="31" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="11" ht="28.5" spans="1:3">
-      <c r="B11" s="30" t="s">
+      <c r="C16" s="32" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="13" ht="18" spans="1:3">
-      <c r="A13" s="31" t="s">
+    <row r="17" spans="1:3" ht="18">
+      <c r="A17" s="33"/>
+      <c r="B17" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="B13" s="31"/>
-    </row>
-    <row r="15" s="23" customFormat="1" ht="18" spans="1:3">
-      <c r="A15" s="32"/>
-      <c r="B15" s="33" t="s">
+    </row>
+    <row r="18" spans="1:3" ht="18">
+      <c r="A18" s="33"/>
+      <c r="B18" s="31" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="16" s="23" customFormat="1" ht="18" spans="1:3">
-      <c r="A16" s="32"/>
-      <c r="B16" s="33" t="s">
+    <row r="19" spans="1:3" ht="18">
+      <c r="A19" s="33"/>
+      <c r="B19" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="C16" s="34" t="s">
+    </row>
+    <row r="20" spans="1:3" s="22" customFormat="1" ht="18">
+      <c r="A20" s="30"/>
+      <c r="B20" s="31" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="17" ht="18" spans="1:3">
-      <c r="A17" s="35"/>
-      <c r="B17" s="33" t="s">
+      <c r="C20" s="34" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="18" ht="18" spans="1:3">
-      <c r="A18" s="35"/>
-      <c r="B18" s="33" t="s">
+    <row r="21" spans="1:3" ht="18">
+      <c r="A21" s="33"/>
+      <c r="B21" s="31" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="19" ht="18" spans="1:3">
-      <c r="A19" s="35"/>
-      <c r="B19" s="33" t="s">
+    <row r="22" spans="1:3" ht="18">
+      <c r="A22" s="33"/>
+      <c r="B22" s="35" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="20" s="23" customFormat="1" ht="18" spans="1:3">
-      <c r="A20" s="32"/>
-      <c r="B20" s="33" t="s">
+    <row r="23" spans="1:3" ht="18">
+      <c r="A23" s="33"/>
+      <c r="B23" s="36"/>
+    </row>
+    <row r="24" spans="1:3" ht="18">
+      <c r="A24" s="120" t="s">
         <v>165</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="B24" s="120"/>
+    </row>
+    <row r="25" spans="1:3" ht="43.5">
+      <c r="A25" s="33"/>
+      <c r="B25" s="31" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="21" ht="18" spans="1:3">
-      <c r="A21" s="35"/>
-      <c r="B21" s="33" t="s">
+    <row r="26" spans="1:3" ht="18">
+      <c r="A26" s="33"/>
+      <c r="B26" s="31"/>
+    </row>
+    <row r="27" spans="1:3" ht="18">
+      <c r="A27" s="33"/>
+      <c r="B27" s="37" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="22" ht="18" spans="1:3">
-      <c r="A22" s="35"/>
-      <c r="B22" s="37" t="s">
+    <row r="28" spans="1:3" ht="18">
+      <c r="A28" s="33"/>
+      <c r="B28" s="31" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="23" ht="18" spans="1:3">
-      <c r="A23" s="35"/>
-      <c r="B23" s="38"/>
-    </row>
-    <row r="24" ht="18" spans="1:3">
-      <c r="A24" s="31" t="s">
+    <row r="29" spans="1:3" ht="28.5">
+      <c r="A29" s="33"/>
+      <c r="B29" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="B24" s="31"/>
-    </row>
-    <row r="25" ht="43.5" spans="1:3">
-      <c r="A25" s="35"/>
-      <c r="B25" s="33" t="s">
+    </row>
+    <row r="30" spans="1:3" ht="18">
+      <c r="A30" s="33"/>
+      <c r="B30" s="31"/>
+    </row>
+    <row r="31" spans="1:3" ht="18">
+      <c r="A31" s="33"/>
+      <c r="B31" s="37" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="26" ht="18" spans="1:3">
-      <c r="A26" s="35"/>
-      <c r="B26" s="33"/>
-    </row>
-    <row r="27" ht="18" spans="1:3">
-      <c r="A27" s="35"/>
-      <c r="B27" s="39" t="s">
+    <row r="32" spans="1:3" ht="18">
+      <c r="A32" s="33"/>
+      <c r="B32" s="31" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="28" ht="18" spans="1:3">
-      <c r="A28" s="35"/>
-      <c r="B28" s="33" t="s">
+    <row r="33" spans="1:2" ht="18">
+      <c r="A33" s="33"/>
+      <c r="B33" s="31" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="29" ht="28.5" spans="1:3">
-      <c r="A29" s="35"/>
-      <c r="B29" s="33" t="s">
+    <row r="34" spans="1:2" ht="18">
+      <c r="A34" s="33"/>
+      <c r="B34" s="36"/>
+    </row>
+    <row r="35" spans="1:2" ht="28.5">
+      <c r="A35" s="33"/>
+      <c r="B35" s="31" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="30" ht="18" spans="1:3">
-      <c r="A30" s="35"/>
-      <c r="B30" s="33"/>
-    </row>
-    <row r="31" ht="18" spans="1:3">
-      <c r="A31" s="35"/>
-      <c r="B31" s="39" t="s">
+    <row r="36" spans="1:2" ht="18">
+      <c r="A36" s="33"/>
+      <c r="B36" s="38" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="32" ht="18" spans="1:3">
-      <c r="A32" s="35"/>
-      <c r="B32" s="33" t="s">
+    <row r="37" spans="1:2" ht="18">
+      <c r="A37" s="33"/>
+      <c r="B37" s="36"/>
+    </row>
+    <row r="38" spans="1:2" ht="18">
+      <c r="A38" s="120" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="33" ht="18" spans="1:2">
-      <c r="A33" s="35"/>
-      <c r="B33" s="33" t="s">
+      <c r="B38" s="120"/>
+    </row>
+    <row r="39" spans="1:2" ht="28.5">
+      <c r="B39" s="31" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="34" ht="18" spans="1:2">
-      <c r="A34" s="35"/>
-      <c r="B34" s="38"/>
-    </row>
-    <row r="35" ht="28.5" spans="1:2">
-      <c r="A35" s="35"/>
-      <c r="B35" s="33" t="s">
+    <row r="41" spans="1:2" ht="14.25">
+      <c r="B41" s="31" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="36" ht="18" spans="1:2">
-      <c r="A36" s="35"/>
-      <c r="B36" s="40" t="s">
+    <row r="43" spans="1:2" ht="28.5">
+      <c r="B43" s="31" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="37" ht="18" spans="1:2">
-      <c r="A37" s="35"/>
-      <c r="B37" s="38"/>
-    </row>
-    <row r="38" ht="18" spans="1:2">
-      <c r="A38" s="31" t="s">
+    <row r="45" spans="1:2" ht="28.5">
+      <c r="B45" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="B38" s="31"/>
-    </row>
-    <row r="39" ht="28.5" spans="1:2">
-      <c r="B39" s="33" t="s">
+    </row>
+    <row r="46" spans="1:2">
+      <c r="B46" s="39"/>
+    </row>
+    <row r="47" spans="1:2" ht="28.5">
+      <c r="B47" s="31" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="41" ht="14.25" spans="1:2">
-      <c r="B41" s="33" t="s">
+    <row r="49" spans="1:2" ht="18">
+      <c r="A49" s="120" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="43" ht="28.5" spans="1:2">
-      <c r="B43" s="33" t="s">
+      <c r="B49" s="120"/>
+    </row>
+    <row r="50" spans="1:2" ht="28.5">
+      <c r="B50" s="31" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="45" ht="28.5" spans="1:2">
-      <c r="B45" s="33" t="s">
+    <row r="52" spans="1:2" ht="14.25">
+      <c r="A52" s="40" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="B46" s="41"/>
-    </row>
-    <row r="47" ht="28.5" spans="1:2">
-      <c r="B47" s="33" t="s">
+      <c r="B52" s="31" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="49" ht="18" spans="1:2">
-      <c r="A49" s="31" t="s">
+    <row r="53" spans="1:2" ht="14.25">
+      <c r="A53" s="40" t="s">
         <v>185</v>
       </c>
-      <c r="B49" s="31"/>
-    </row>
-    <row r="50" ht="28.5" spans="1:2">
-      <c r="B50" s="33" t="s">
+      <c r="B53" s="31" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="52" ht="14.25" spans="1:2">
-      <c r="A52" s="42" t="s">
+    <row r="54" spans="1:2" ht="14.25">
+      <c r="A54" s="40" t="s">
         <v>187</v>
       </c>
-      <c r="B52" s="33" t="s">
+      <c r="B54" s="31" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="53" ht="14.25" spans="1:2">
-      <c r="A53" s="42" t="s">
+    <row r="55" spans="1:2" ht="28.5">
+      <c r="A55" s="29"/>
+      <c r="B55" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="B53" s="33" t="s">
+    </row>
+    <row r="56" spans="1:2" ht="28.5">
+      <c r="A56" s="29"/>
+      <c r="B56" s="31" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="54" ht="14.25" spans="1:2">
-      <c r="A54" s="42" t="s">
+    <row r="57" spans="1:2" ht="14.25">
+      <c r="A57" s="40" t="s">
         <v>191</v>
       </c>
-      <c r="B54" s="33" t="s">
+      <c r="B57" s="31" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="55" ht="28.5" spans="1:2">
-      <c r="A55" s="30"/>
-      <c r="B55" s="33" t="s">
+    <row r="58" spans="1:2" ht="14.25">
+      <c r="A58" s="29"/>
+      <c r="B58" s="31" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="56" ht="28.5" spans="1:2">
-      <c r="A56" s="30"/>
-      <c r="B56" s="33" t="s">
+    <row r="59" spans="1:2" ht="14.25">
+      <c r="A59" s="29"/>
+      <c r="B59" s="31" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="57" ht="14.25" spans="1:2">
-      <c r="A57" s="42" t="s">
+    <row r="60" spans="1:2" ht="14.25">
+      <c r="A60" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="B57" s="33" t="s">
+      <c r="B60" s="31" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="58" ht="14.25" spans="1:2">
-      <c r="A58" s="30"/>
-      <c r="B58" s="33" t="s">
+    <row r="61" spans="1:2" ht="28.5">
+      <c r="A61" s="29"/>
+      <c r="B61" s="31" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="59" ht="14.25" spans="1:2">
-      <c r="A59" s="30"/>
-      <c r="B59" s="33" t="s">
+    <row r="62" spans="1:2" ht="14.25">
+      <c r="A62" s="40" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="60" ht="14.25" spans="1:2">
-      <c r="A60" s="42" t="s">
+      <c r="B62" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="B60" s="33" t="s">
+    </row>
+    <row r="63" spans="1:2" ht="14.25">
+      <c r="A63" s="41"/>
+      <c r="B63" s="31" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="61" ht="28.5" spans="1:2">
-      <c r="A61" s="30"/>
-      <c r="B61" s="33" t="s">
+    <row r="64" spans="1:2">
+      <c r="B64" s="42"/>
+    </row>
+    <row r="65" spans="1:2" ht="18">
+      <c r="A65" s="120" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="62" ht="14.25" spans="1:2">
-      <c r="A62" s="42" t="s">
+      <c r="B65" s="120"/>
+    </row>
+    <row r="66" spans="1:2" ht="42.75">
+      <c r="B66" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="B62" s="33" t="s">
+    </row>
+    <row r="68" spans="1:2" ht="18">
+      <c r="A68" s="120" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="63" ht="14.25" spans="1:2">
-      <c r="A63" s="43"/>
-      <c r="B63" s="33" t="s">
+      <c r="B68" s="120"/>
+    </row>
+    <row r="69" spans="1:2" ht="15">
+      <c r="A69" s="43" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="B64" s="44"/>
-    </row>
-    <row r="65" ht="18" spans="1:2">
-      <c r="A65" s="31" t="s">
+      <c r="B69" s="44" t="s">
         <v>205</v>
       </c>
-      <c r="B65" s="31"/>
-    </row>
-    <row r="66" ht="42.75" spans="1:2">
-      <c r="B66" s="33" t="s">
+    </row>
+    <row r="70" spans="1:2" ht="28.5">
+      <c r="A70" s="41"/>
+      <c r="B70" s="45" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="68" ht="18" spans="1:2">
-      <c r="A68" s="31" t="s">
+    <row r="71" spans="1:2" ht="14.25">
+      <c r="A71" s="41"/>
+      <c r="B71" s="46"/>
+    </row>
+    <row r="72" spans="1:2" ht="15">
+      <c r="A72" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="B72" s="44" t="s">
         <v>207</v>
       </c>
-      <c r="B68" s="31"/>
-    </row>
-    <row r="69" ht="15" spans="1:2">
-      <c r="A69" s="45" t="s">
+    </row>
+    <row r="73" spans="1:2" ht="28.5">
+      <c r="A73" s="41"/>
+      <c r="B73" s="45" t="s">
         <v>208</v>
       </c>
-      <c r="B69" s="46" t="s">
+    </row>
+    <row r="74" spans="1:2" ht="14.25">
+      <c r="A74" s="41"/>
+      <c r="B74" s="46"/>
+    </row>
+    <row r="75" spans="1:2" ht="15">
+      <c r="A75" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="B75" s="47" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="70" ht="28.5" spans="1:2">
-      <c r="A70" s="43"/>
-      <c r="B70" s="47" t="s">
+    <row r="76" spans="1:2" ht="42.75">
+      <c r="A76" s="41"/>
+      <c r="B76" s="28" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="71" ht="14.25" spans="1:2">
-      <c r="A71" s="43"/>
-      <c r="B71" s="48"/>
-    </row>
-    <row r="72" ht="15" spans="1:2">
-      <c r="A72" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="B72" s="46" t="s">
+    <row r="77" spans="1:2" ht="14.25">
+      <c r="A77" s="41"/>
+      <c r="B77" s="41"/>
+    </row>
+    <row r="78" spans="1:2" ht="15">
+      <c r="A78" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="B78" s="47" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="73" ht="28.5" spans="1:2">
-      <c r="A73" s="43"/>
-      <c r="B73" s="47" t="s">
+    <row r="79" spans="1:2" ht="28.5">
+      <c r="A79" s="41"/>
+      <c r="B79" s="28" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="74" ht="14.25" spans="1:2">
-      <c r="A74" s="43"/>
-      <c r="B74" s="48"/>
-    </row>
-    <row r="75" ht="15" spans="1:2">
-      <c r="A75" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="B75" s="49" t="s">
+    <row r="80" spans="1:2" ht="14.25">
+      <c r="A80" s="41"/>
+      <c r="B80" s="41"/>
+    </row>
+    <row r="81" spans="1:2" ht="15">
+      <c r="A81" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="B81" s="47" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="76" ht="42.75" spans="1:2">
-      <c r="A76" s="43"/>
-      <c r="B76" s="29" t="s">
+    <row r="82" spans="1:2" ht="14.25">
+      <c r="A82" s="41"/>
+      <c r="B82" s="48" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="77" ht="14.25" spans="1:2">
-      <c r="A77" s="43"/>
-      <c r="B77" s="43"/>
-    </row>
-    <row r="78" ht="15" spans="1:2">
-      <c r="A78" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="B78" s="49" t="s">
+    <row r="83" spans="1:2" ht="14.25">
+      <c r="A83" s="41"/>
+      <c r="B83" s="48" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="79" ht="28.5" spans="1:2">
-      <c r="A79" s="43"/>
-      <c r="B79" s="29" t="s">
+    <row r="84" spans="1:2" ht="14.25">
+      <c r="A84" s="41"/>
+      <c r="B84" s="48" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="80" ht="14.25" spans="1:2">
-      <c r="A80" s="43"/>
-      <c r="B80" s="43"/>
-    </row>
-    <row r="81" ht="15" spans="1:2">
-      <c r="A81" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="B81" s="49" t="s">
+    <row r="85" spans="1:2" ht="15">
+      <c r="A85" s="41"/>
+      <c r="B85" s="49"/>
+    </row>
+    <row r="86" spans="1:2" ht="15">
+      <c r="A86" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="B86" s="47" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="82" ht="14.25" spans="1:2">
-      <c r="A82" s="43"/>
-      <c r="B82" s="50" t="s">
+    <row r="87" spans="1:2" ht="42.75">
+      <c r="A87" s="41"/>
+      <c r="B87" s="28" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="83" ht="14.25" spans="1:2">
-      <c r="A83" s="43"/>
-      <c r="B83" s="50" t="s">
+    <row r="88" spans="1:2" ht="14.25">
+      <c r="A88" s="41"/>
+      <c r="B88" s="109" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="84" ht="14.25" spans="1:2">
-      <c r="A84" s="43"/>
-      <c r="B84" s="50" t="s">
+    <row r="89" spans="1:2" ht="57">
+      <c r="A89" s="41"/>
+      <c r="B89" s="110" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="85" ht="15" spans="1:2">
-      <c r="A85" s="43"/>
-      <c r="B85" s="51"/>
-    </row>
-    <row r="86" ht="15" spans="1:2">
-      <c r="A86" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="B86" s="49" t="s">
+    <row r="90" spans="1:2" ht="14.25">
+      <c r="A90" s="41"/>
+      <c r="B90" s="41"/>
+    </row>
+    <row r="91" spans="1:2" ht="15">
+      <c r="A91" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="B91" s="47" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="87" ht="42.75" spans="1:2">
-      <c r="A87" s="43"/>
-      <c r="B87" s="29" t="s">
+    <row r="92" spans="1:2" ht="28.5">
+      <c r="A92" s="29"/>
+      <c r="B92" s="48" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="88" ht="14.25" spans="1:2">
-      <c r="A88" s="43"/>
-      <c r="B88" s="121" t="s">
+    <row r="94" spans="1:2">
+      <c r="A94" s="50" t="s">
         <v>223</v>
-      </c>
-    </row>
-    <row r="89" ht="57" spans="1:2">
-      <c r="A89" s="43"/>
-      <c r="B89" s="122" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="90" ht="14.25" spans="1:2">
-      <c r="A90" s="43"/>
-      <c r="B90" s="43"/>
-    </row>
-    <row r="91" ht="15" spans="1:2">
-      <c r="A91" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="B91" s="49" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="92" ht="28.5" spans="1:2">
-      <c r="A92" s="30"/>
-      <c r="B92" s="50" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" s="53" t="s">
-        <v>227</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A68:B68"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A68:B68"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B9" r:id="rId4" display="Watch Demo Videos of the Pro Version on Vertex42.com"/>
-    <hyperlink ref="A2" r:id="rId5" display="https://www.vertex42.com/ExcelTemplates/excel-gantt-chart.html"/>
-    <hyperlink ref="B36" r:id="rId6" display="Help improve Excel by voting on a suggestion to fix this problem."/>
+    <hyperlink ref="B9" r:id="rId1"/>
+    <hyperlink ref="A2" r:id="rId2"/>
+    <hyperlink ref="B36" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.25" bottom="0.25" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="8.85714285714286" defaultRowHeight="12.75" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
-    <col min="2" max="2" width="82.1428571428571" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="82.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:3" ht="30" customHeight="1">
+      <c r="A1" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="B1" s="12"/>
+    </row>
+    <row r="2" spans="1:3" ht="15">
+      <c r="B2" s="13"/>
+    </row>
+    <row r="3" spans="1:3" ht="15">
+      <c r="A3" s="14"/>
+      <c r="B3" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C3" s="14"/>
+    </row>
+    <row r="4" spans="1:3" ht="14.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="16"/>
+    </row>
+    <row r="5" spans="1:3" ht="15">
+      <c r="A5" s="16"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="16"/>
+    </row>
+    <row r="6" spans="1:3" ht="15.75">
+      <c r="A6" s="16"/>
+      <c r="B6" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:3" ht="15">
+      <c r="A7" s="16"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8" spans="1:3" ht="30">
+      <c r="A8" s="16"/>
+      <c r="B8" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" s="16"/>
+    </row>
+    <row r="9" spans="1:3" ht="15">
+      <c r="A9" s="16"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="16"/>
+    </row>
+    <row r="10" spans="1:3" ht="46.5">
+      <c r="A10" s="16"/>
+      <c r="B10" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="16"/>
+    </row>
+    <row r="11" spans="1:3" ht="15">
+      <c r="A11" s="16"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="16"/>
+    </row>
+    <row r="12" spans="1:3" ht="45">
+      <c r="A12" s="16"/>
+      <c r="B12" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="13"/>
-    </row>
-    <row r="2" ht="15" spans="1:3">
-      <c r="B2" s="14"/>
-    </row>
-    <row r="3" ht="15" spans="1:3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="16" t="s">
+      <c r="C12" s="16"/>
+    </row>
+    <row r="13" spans="1:3" ht="15">
+      <c r="A13" s="16"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="16"/>
+    </row>
+    <row r="14" spans="1:3" ht="60">
+      <c r="A14" s="16"/>
+      <c r="B14" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="15"/>
-    </row>
-    <row r="4" ht="14.25" spans="1:3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="C4" s="17"/>
-    </row>
-    <row r="5" ht="15" spans="1:3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="17"/>
-    </row>
-    <row r="6" ht="15.75" spans="1:3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="C6" s="17"/>
-    </row>
-    <row r="7" ht="15" spans="1:3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="17"/>
-    </row>
-    <row r="8" ht="30" spans="1:3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="19" t="s">
+      <c r="C14" s="16"/>
+    </row>
+    <row r="15" spans="1:3" ht="15">
+      <c r="A15" s="16"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="16"/>
+    </row>
+    <row r="16" spans="1:3" ht="30.75">
+      <c r="A16" s="16"/>
+      <c r="B16" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="C8" s="17"/>
-    </row>
-    <row r="9" ht="15" spans="1:3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="17"/>
-    </row>
-    <row r="10" ht="46.5" spans="1:3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="19" t="s">
+      <c r="C16" s="16"/>
+    </row>
+    <row r="17" spans="1:3" ht="15">
+      <c r="A17" s="16"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="16"/>
+    </row>
+    <row r="18" spans="1:3" ht="15.75">
+      <c r="A18" s="16"/>
+      <c r="B18" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="C10" s="17"/>
-    </row>
-    <row r="11" ht="15" spans="1:3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="17"/>
-    </row>
-    <row r="12" ht="45" spans="1:3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="19" t="s">
+      <c r="C18" s="16"/>
+    </row>
+    <row r="19" spans="1:3" ht="15">
+      <c r="A19" s="16"/>
+      <c r="B19" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="C12" s="17"/>
-    </row>
-    <row r="13" ht="15" spans="1:3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="17"/>
-    </row>
-    <row r="14" ht="60" spans="1:3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="C14" s="17"/>
-    </row>
-    <row r="15" ht="15" spans="1:3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="17"/>
-    </row>
-    <row r="16" ht="30.75" spans="1:3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="C16" s="17"/>
-    </row>
-    <row r="17" ht="15" spans="1:3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="17"/>
-    </row>
-    <row r="18" ht="15.75" spans="1:3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="C18" s="17"/>
-    </row>
-    <row r="19" ht="15" spans="1:3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="C19" s="17"/>
-    </row>
-    <row r="20" ht="15" spans="1:3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="17"/>
+      <c r="C19" s="16"/>
+    </row>
+    <row r="20" spans="1:3" ht="15">
+      <c r="A20" s="16"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="16"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId2" display="https://www.vertex42.com/ExcelTemplates/excel-gantt-chart.html"/>
-    <hyperlink ref="B19" r:id="rId3" display="https://www.vertex42.com/licensing/EULA_privateuse.html"/>
+    <hyperlink ref="B4" r:id="rId1"/>
+    <hyperlink ref="B19" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="49.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="49.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="37.5" customHeight="1" spans="1:13">
-      <c r="A1" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
+    <row r="1" spans="1:13" ht="37.5" customHeight="1">
+      <c r="A1" s="121" t="s">
+        <v>233</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -16484,65 +15928,63 @@
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BN22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="66.1428571428571" customWidth="1"/>
+    <col min="1" max="1" width="66.140625" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:66">
+    <row r="1" spans="1:66" ht="15">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" ht="15" spans="1:66">
+    <row r="2" spans="1:66" ht="15">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" ht="15" spans="1:66">
+    <row r="3" spans="1:66" ht="15">
       <c r="A3" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B3" s="3"/>
     </row>
-    <row r="4" ht="15" spans="1:66">
+    <row r="4" spans="1:66" ht="15">
       <c r="A4" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B4" s="3"/>
     </row>
-    <row r="5" ht="15" spans="1:66">
+    <row r="5" spans="1:66" ht="15">
       <c r="A5" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:66">
       <c r="A6" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:66">
       <c r="A7" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="18" spans="1:66">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A13" s="4" t="str">
         <f>IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"0.1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),prevWBS&amp;".1",LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1)))&amp;IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",2))),VALUE(RIGHT(prevWBS,LEN(prevWBS)-FIND("`",SUBSTITUTE(prevWBS,".","`",1))))+1,VALUE(MID(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))+1,(FIND("`",SUBSTITUTE(prevWBS,".","`",2))-FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1)))+1)))</f>
         <v>0.1</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -16550,11 +15992,11 @@
       <c r="D13" s="5"/>
       <c r="E13" s="6">
         <f>GanttChart!F59+1</f>
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="F13" s="7">
         <f t="shared" ref="F13:F17" si="0">IF(ISBLANK(E13)," - ",IF(G13=0,E13,E13+G13-1))</f>
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="G13" s="8">
         <v>2</v>
@@ -16564,7 +16006,7 @@
       </c>
       <c r="I13" s="10">
         <f t="shared" ref="I13:I17" si="1">IF(OR(F13=0,E13=0)," - ",NETWORKDAYS(E13,F13))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="11"/>
       <c r="K13" s="4"/>
@@ -16624,13 +16066,13 @@
       <c r="BM13" s="4"/>
       <c r="BN13" s="4"/>
     </row>
-    <row r="14" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="14" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A14" s="4" t="str">
         <f>IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"0.1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),prevWBS&amp;".1",LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1)))&amp;IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",2))),VALUE(RIGHT(prevWBS,LEN(prevWBS)-FIND("`",SUBSTITUTE(prevWBS,".","`",1))))+1,VALUE(MID(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))+1,(FIND("`",SUBSTITUTE(prevWBS,".","`",2))-FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1)))+1)))</f>
         <v>0.2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>20</v>
@@ -16638,11 +16080,11 @@
       <c r="D14" s="5"/>
       <c r="E14" s="6">
         <f>GanttChart!F60+1</f>
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="F14" s="7">
         <f t="shared" si="0"/>
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="G14" s="8">
         <v>4</v>
@@ -16652,7 +16094,7 @@
       </c>
       <c r="I14" s="10">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14" s="11"/>
       <c r="K14" s="4"/>
@@ -16712,13 +16154,13 @@
       <c r="BM14" s="4"/>
       <c r="BN14" s="4"/>
     </row>
-    <row r="15" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="15" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A15" s="4" t="str">
         <f>IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"0.1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),prevWBS&amp;".1",LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1)))&amp;IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",2))),VALUE(RIGHT(prevWBS,LEN(prevWBS)-FIND("`",SUBSTITUTE(prevWBS,".","`",1))))+1,VALUE(MID(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))+1,(FIND("`",SUBSTITUTE(prevWBS,".","`",2))-FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1)))+1)))</f>
         <v>0.3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -16726,11 +16168,11 @@
       <c r="D15" s="5"/>
       <c r="E15" s="6">
         <f t="shared" ref="E15:E17" si="2">F13+1</f>
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="F15" s="7">
         <f t="shared" si="0"/>
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="G15" s="8">
         <v>4</v>
@@ -16740,7 +16182,7 @@
       </c>
       <c r="I15" s="10">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="4"/>
@@ -16800,13 +16242,13 @@
       <c r="BM15" s="4"/>
       <c r="BN15" s="4"/>
     </row>
-    <row r="16" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="16" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A16" s="4" t="str">
         <f>IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"0.1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),prevWBS&amp;".1",LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1)))&amp;IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",2))),VALUE(RIGHT(prevWBS,LEN(prevWBS)-FIND("`",SUBSTITUTE(prevWBS,".","`",1))))+1,VALUE(MID(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))+1,(FIND("`",SUBSTITUTE(prevWBS,".","`",2))-FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1)))+1)))</f>
         <v>0.4</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>20</v>
@@ -16814,11 +16256,11 @@
       <c r="D16" s="5"/>
       <c r="E16" s="6">
         <f t="shared" si="2"/>
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="F16" s="7">
         <f t="shared" si="0"/>
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="G16" s="8">
         <v>2</v>
@@ -16828,7 +16270,7 @@
       </c>
       <c r="I16" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="11"/>
       <c r="K16" s="4"/>
@@ -16888,13 +16330,13 @@
       <c r="BM16" s="4"/>
       <c r="BN16" s="4"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="18" spans="1:66">
+    <row r="17" spans="1:66" s="1" customFormat="1" ht="18">
       <c r="A17" s="4" t="str">
         <f>IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"0.1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),prevWBS&amp;".1",LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1)))&amp;IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",2))),VALUE(RIGHT(prevWBS,LEN(prevWBS)-FIND("`",SUBSTITUTE(prevWBS,".","`",1))))+1,VALUE(MID(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))+1,(FIND("`",SUBSTITUTE(prevWBS,".","`",2))-FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1)))+1)))</f>
         <v>0.5</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -16902,11 +16344,11 @@
       <c r="D17" s="5"/>
       <c r="E17" s="6">
         <f t="shared" si="2"/>
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="F17" s="7">
         <f t="shared" si="0"/>
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="G17" s="8">
         <v>2</v>
@@ -16916,7 +16358,7 @@
       </c>
       <c r="I17" s="10">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="4"/>
@@ -16978,7 +16420,7 @@
     </row>
     <row r="22" spans="1:66">
       <c r="A22" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -16987,11 +16429,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bae600e7-fe4a-406d-a0a0-d49ad13af25e}</x14:id>
+          <x14:id>{BAE600E7-FE4A-406D-A0A0-D49AD13AF25E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -17001,11 +16443,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5c19d324-34a6-430a-912b-754b3a96cbe3}</x14:id>
+          <x14:id>{5C19D324-34A6-430A-912B-754B3A96CBE3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -17015,11 +16457,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{defbed01-472b-49d5-9ec8-a70152298a6c}</x14:id>
+          <x14:id>{DEFBED01-472B-49D5-9EC8-A70152298A6C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -17029,11 +16471,11 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8a0fc972-e9c5-456e-b171-44cef3a11daf}</x14:id>
+          <x14:id>{8A0FC972-E9C5-456E-B171-44CEF3A11DAF}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -17043,33 +16485,32 @@
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e031bc06-22b7-4628-bb42-6bbec0c7fed9}</x14:id>
+          <x14:id>{E031BC06-22B7-4628-BB42-6BBEC0C7FED9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13:BN17">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>K$6=TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>AND($E13&lt;=K$6,ROUNDDOWN(($F13-$E13+1)*$H13,0)+$E13-1&gt;=K$6)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>AND(NOT(ISBLANK($E13)),$E13&lt;=K$6,$F13&gt;=K$6)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bae600e7-fe4a-406d-a0a0-d49ad13af25e}">
+          <x14:cfRule type="dataBar" id="{BAE600E7-FE4A-406D-A0A0-D49AD13AF25E}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -17084,7 +16525,7 @@
           <xm:sqref>H13</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5c19d324-34a6-430a-912b-754b3a96cbe3}">
+          <x14:cfRule type="dataBar" id="{5C19D324-34A6-430A-912B-754B3A96CBE3}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -17099,7 +16540,7 @@
           <xm:sqref>H14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{defbed01-472b-49d5-9ec8-a70152298a6c}">
+          <x14:cfRule type="dataBar" id="{DEFBED01-472B-49D5-9EC8-A70152298A6C}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -17114,7 +16555,7 @@
           <xm:sqref>H15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8a0fc972-e9c5-456e-b171-44cef3a11daf}">
+          <x14:cfRule type="dataBar" id="{8A0FC972-E9C5-456E-B171-44CEF3A11DAF}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -17129,7 +16570,7 @@
           <xm:sqref>H16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e031bc06-22b7-4628-bb42-6bbec0c7fed9}">
+          <x14:cfRule type="dataBar" id="{E031BC06-22B7-4628-BB42-6BBEC0C7FED9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/Gantt-chart TIMELINE per 3 Maret 2026 rev_1.xlsx
+++ b/Gantt-chart TIMELINE per 3 Maret 2026 rev_1.xlsx
@@ -852,7 +852,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="245">
   <si>
     <t>RICEF BY LEUWITEX ( update 3 Maret 2026 )</t>
   </si>
@@ -2331,17 +2331,29 @@
   <si>
     <t>Libur lebaran 18-26 February</t>
   </si>
+  <si>
+    <t>Stock Per Barcode sudah selesai</t>
+  </si>
+  <si>
+    <t>Stock Leadtime sudah selesai</t>
+  </si>
+  <si>
+    <t>List Karton per kode order sudah selesai</t>
+  </si>
+  <si>
+    <t>Packing Lead Time sudah selesai</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="5">
-    <numFmt numFmtId="166" formatCode="ddd\ m/dd/yy"/>
-    <numFmt numFmtId="167" formatCode="m/d/yyyy\ \(dddd\)"/>
-    <numFmt numFmtId="168" formatCode="d\ mmm\ yyyy"/>
-    <numFmt numFmtId="169" formatCode="d"/>
-    <numFmt numFmtId="170" formatCode="ddd\ dd/m/yy"/>
+    <numFmt numFmtId="164" formatCode="ddd\ m/dd/yy"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy\ \(dddd\)"/>
+    <numFmt numFmtId="166" formatCode="d\ mmm\ yyyy"/>
+    <numFmt numFmtId="167" formatCode="d"/>
+    <numFmt numFmtId="168" formatCode="ddd\ dd/m/yy"/>
   </numFmts>
   <fonts count="51">
     <font>
@@ -2949,10 +2961,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3110,13 +3122,13 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3152,10 +3164,10 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="1" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="1" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="1" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="1" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="5" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3215,7 +3227,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3239,10 +3251,28 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="34" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="34" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="34" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="34" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
@@ -3255,36 +3285,18 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="34" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="168" fontId="34" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="34" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="34" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4194,27 +4206,27 @@
       <c r="E1" s="57"/>
       <c r="F1" s="57"/>
       <c r="I1" s="58"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
-      <c r="V1" s="111"/>
-      <c r="W1" s="111"/>
-      <c r="X1" s="111"/>
-      <c r="Y1" s="111"/>
-      <c r="Z1" s="111"/>
-      <c r="AA1" s="111"/>
-      <c r="AB1" s="111"/>
-      <c r="AC1" s="111"/>
-      <c r="AD1" s="111"/>
-      <c r="AE1" s="111"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
+      <c r="AC1" s="122"/>
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="122"/>
     </row>
     <row r="2" spans="1:66" ht="18" customHeight="1">
       <c r="A2" s="59"/>
@@ -4251,11 +4263,11 @@
       <c r="B4" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="112">
+      <c r="C4" s="123">
         <v>45986</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
       <c r="F4" s="65"/>
       <c r="G4" s="66" t="s">
         <v>2</v>
@@ -4264,182 +4276,182 @@
         <v>1</v>
       </c>
       <c r="J4" s="65"/>
-      <c r="K4" s="113" t="str">
+      <c r="K4" s="119" t="str">
         <f>"Week "&amp;(K6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 1</v>
       </c>
-      <c r="L4" s="114"/>
-      <c r="M4" s="114"/>
-      <c r="N4" s="114"/>
-      <c r="O4" s="114"/>
-      <c r="P4" s="114"/>
-      <c r="Q4" s="115"/>
-      <c r="R4" s="113" t="str">
+      <c r="L4" s="120"/>
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120"/>
+      <c r="P4" s="120"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="119" t="str">
         <f>"Week "&amp;(R6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 2</v>
       </c>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114"/>
-      <c r="V4" s="114"/>
-      <c r="W4" s="114"/>
-      <c r="X4" s="115"/>
-      <c r="Y4" s="113" t="str">
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
+      <c r="U4" s="120"/>
+      <c r="V4" s="120"/>
+      <c r="W4" s="120"/>
+      <c r="X4" s="121"/>
+      <c r="Y4" s="119" t="str">
         <f>"Week "&amp;(Y6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 3</v>
       </c>
-      <c r="Z4" s="114"/>
-      <c r="AA4" s="114"/>
-      <c r="AB4" s="114"/>
-      <c r="AC4" s="114"/>
-      <c r="AD4" s="114"/>
-      <c r="AE4" s="115"/>
-      <c r="AF4" s="113" t="str">
+      <c r="Z4" s="120"/>
+      <c r="AA4" s="120"/>
+      <c r="AB4" s="120"/>
+      <c r="AC4" s="120"/>
+      <c r="AD4" s="120"/>
+      <c r="AE4" s="121"/>
+      <c r="AF4" s="119" t="str">
         <f>"Week "&amp;(AF6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 4</v>
       </c>
-      <c r="AG4" s="114"/>
-      <c r="AH4" s="114"/>
-      <c r="AI4" s="114"/>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114"/>
-      <c r="AL4" s="115"/>
-      <c r="AM4" s="113" t="str">
+      <c r="AG4" s="120"/>
+      <c r="AH4" s="120"/>
+      <c r="AI4" s="120"/>
+      <c r="AJ4" s="120"/>
+      <c r="AK4" s="120"/>
+      <c r="AL4" s="121"/>
+      <c r="AM4" s="119" t="str">
         <f>"Week "&amp;(AM6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AN4" s="114"/>
-      <c r="AO4" s="114"/>
-      <c r="AP4" s="114"/>
-      <c r="AQ4" s="114"/>
-      <c r="AR4" s="114"/>
-      <c r="AS4" s="115"/>
-      <c r="AT4" s="113" t="str">
+      <c r="AN4" s="120"/>
+      <c r="AO4" s="120"/>
+      <c r="AP4" s="120"/>
+      <c r="AQ4" s="120"/>
+      <c r="AR4" s="120"/>
+      <c r="AS4" s="121"/>
+      <c r="AT4" s="119" t="str">
         <f>"Week "&amp;(AT6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AU4" s="114"/>
-      <c r="AV4" s="114"/>
-      <c r="AW4" s="114"/>
-      <c r="AX4" s="114"/>
-      <c r="AY4" s="114"/>
-      <c r="AZ4" s="115"/>
-      <c r="BA4" s="113" t="str">
+      <c r="AU4" s="120"/>
+      <c r="AV4" s="120"/>
+      <c r="AW4" s="120"/>
+      <c r="AX4" s="120"/>
+      <c r="AY4" s="120"/>
+      <c r="AZ4" s="121"/>
+      <c r="BA4" s="119" t="str">
         <f>"Week "&amp;(BA6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 7</v>
       </c>
-      <c r="BB4" s="114"/>
-      <c r="BC4" s="114"/>
-      <c r="BD4" s="114"/>
-      <c r="BE4" s="114"/>
-      <c r="BF4" s="114"/>
-      <c r="BG4" s="115"/>
-      <c r="BH4" s="113" t="str">
+      <c r="BB4" s="120"/>
+      <c r="BC4" s="120"/>
+      <c r="BD4" s="120"/>
+      <c r="BE4" s="120"/>
+      <c r="BF4" s="120"/>
+      <c r="BG4" s="121"/>
+      <c r="BH4" s="119" t="str">
         <f>"Week "&amp;(BH6-($C$4-WEEKDAY($C$4,1)+2))/7+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BI4" s="114"/>
-      <c r="BJ4" s="114"/>
-      <c r="BK4" s="114"/>
-      <c r="BL4" s="114"/>
-      <c r="BM4" s="114"/>
-      <c r="BN4" s="115"/>
+      <c r="BI4" s="120"/>
+      <c r="BJ4" s="120"/>
+      <c r="BK4" s="120"/>
+      <c r="BL4" s="120"/>
+      <c r="BM4" s="120"/>
+      <c r="BN4" s="121"/>
     </row>
     <row r="5" spans="1:66" ht="17.25" customHeight="1">
       <c r="A5" s="65"/>
       <c r="B5" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="116" t="s">
+      <c r="C5" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
       <c r="F5" s="65"/>
       <c r="G5" s="65"/>
       <c r="H5" s="65"/>
       <c r="I5" s="65"/>
       <c r="J5" s="65"/>
-      <c r="K5" s="117">
+      <c r="K5" s="115">
         <f>K6</f>
         <v>45985</v>
       </c>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
-      <c r="O5" s="118"/>
-      <c r="P5" s="118"/>
-      <c r="Q5" s="119"/>
-      <c r="R5" s="117">
+      <c r="L5" s="116"/>
+      <c r="M5" s="116"/>
+      <c r="N5" s="116"/>
+      <c r="O5" s="116"/>
+      <c r="P5" s="116"/>
+      <c r="Q5" s="117"/>
+      <c r="R5" s="115">
         <f>R6</f>
         <v>45992</v>
       </c>
-      <c r="S5" s="118"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="118"/>
-      <c r="W5" s="118"/>
-      <c r="X5" s="119"/>
-      <c r="Y5" s="117">
+      <c r="S5" s="116"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="116"/>
+      <c r="V5" s="116"/>
+      <c r="W5" s="116"/>
+      <c r="X5" s="117"/>
+      <c r="Y5" s="115">
         <f>Y6</f>
         <v>45999</v>
       </c>
-      <c r="Z5" s="118"/>
-      <c r="AA5" s="118"/>
-      <c r="AB5" s="118"/>
-      <c r="AC5" s="118"/>
-      <c r="AD5" s="118"/>
-      <c r="AE5" s="119"/>
-      <c r="AF5" s="117">
+      <c r="Z5" s="116"/>
+      <c r="AA5" s="116"/>
+      <c r="AB5" s="116"/>
+      <c r="AC5" s="116"/>
+      <c r="AD5" s="116"/>
+      <c r="AE5" s="117"/>
+      <c r="AF5" s="115">
         <f>AF6</f>
         <v>46006</v>
       </c>
-      <c r="AG5" s="118"/>
-      <c r="AH5" s="118"/>
-      <c r="AI5" s="118"/>
-      <c r="AJ5" s="118"/>
-      <c r="AK5" s="118"/>
-      <c r="AL5" s="119"/>
-      <c r="AM5" s="117">
+      <c r="AG5" s="116"/>
+      <c r="AH5" s="116"/>
+      <c r="AI5" s="116"/>
+      <c r="AJ5" s="116"/>
+      <c r="AK5" s="116"/>
+      <c r="AL5" s="117"/>
+      <c r="AM5" s="115">
         <f>AM6</f>
         <v>46013</v>
       </c>
-      <c r="AN5" s="118"/>
-      <c r="AO5" s="118"/>
-      <c r="AP5" s="118"/>
-      <c r="AQ5" s="118"/>
-      <c r="AR5" s="118"/>
-      <c r="AS5" s="119"/>
-      <c r="AT5" s="117">
+      <c r="AN5" s="116"/>
+      <c r="AO5" s="116"/>
+      <c r="AP5" s="116"/>
+      <c r="AQ5" s="116"/>
+      <c r="AR5" s="116"/>
+      <c r="AS5" s="117"/>
+      <c r="AT5" s="115">
         <f>AT6</f>
         <v>46020</v>
       </c>
-      <c r="AU5" s="118"/>
-      <c r="AV5" s="118"/>
-      <c r="AW5" s="118"/>
-      <c r="AX5" s="118"/>
-      <c r="AY5" s="118"/>
-      <c r="AZ5" s="119"/>
-      <c r="BA5" s="117">
+      <c r="AU5" s="116"/>
+      <c r="AV5" s="116"/>
+      <c r="AW5" s="116"/>
+      <c r="AX5" s="116"/>
+      <c r="AY5" s="116"/>
+      <c r="AZ5" s="117"/>
+      <c r="BA5" s="115">
         <f>BA6</f>
         <v>46027</v>
       </c>
-      <c r="BB5" s="118"/>
-      <c r="BC5" s="118"/>
-      <c r="BD5" s="118"/>
-      <c r="BE5" s="118"/>
-      <c r="BF5" s="118"/>
-      <c r="BG5" s="119"/>
-      <c r="BH5" s="117">
+      <c r="BB5" s="116"/>
+      <c r="BC5" s="116"/>
+      <c r="BD5" s="116"/>
+      <c r="BE5" s="116"/>
+      <c r="BF5" s="116"/>
+      <c r="BG5" s="117"/>
+      <c r="BH5" s="115">
         <f>BH6</f>
         <v>46034</v>
       </c>
-      <c r="BI5" s="118"/>
-      <c r="BJ5" s="118"/>
-      <c r="BK5" s="118"/>
-      <c r="BL5" s="118"/>
-      <c r="BM5" s="118"/>
-      <c r="BN5" s="119"/>
+      <c r="BI5" s="116"/>
+      <c r="BJ5" s="116"/>
+      <c r="BK5" s="116"/>
+      <c r="BL5" s="116"/>
+      <c r="BM5" s="116"/>
+      <c r="BN5" s="117"/>
     </row>
     <row r="6" spans="1:66">
       <c r="A6" s="65"/>
@@ -5120,7 +5132,7 @@
         <v>67</v>
       </c>
       <c r="H10" s="9">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I10" s="10">
         <f>IF(OR(F10=0,E10=0)," - ",NETWORKDAYS(E10,F10))</f>
@@ -7395,7 +7407,7 @@
         <v>4</v>
       </c>
       <c r="H36" s="9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I36" s="10">
         <f t="shared" si="18"/>
@@ -7747,7 +7759,7 @@
         <v>2</v>
       </c>
       <c r="H40" s="9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" ref="I40:I60" si="34">IF(OR(F40=0,E40=0)," - ",NETWORKDAYS(E40,F40))</f>
@@ -8011,7 +8023,7 @@
         <v>3</v>
       </c>
       <c r="H43" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="10">
         <f t="shared" si="34"/>
@@ -8099,7 +8111,7 @@
         <v>3</v>
       </c>
       <c r="H44" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="10">
         <f t="shared" si="34"/>
@@ -8440,7 +8452,7 @@
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="6">
-        <f t="shared" ref="E48:E55" si="37">F46+1</f>
+        <f t="shared" ref="E48:E53" si="37">F46+1</f>
         <v>46091</v>
       </c>
       <c r="F48" s="7">
@@ -9331,7 +9343,7 @@
         <v>2</v>
       </c>
       <c r="H58" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" s="10">
         <f t="shared" si="34"/>
@@ -9575,10 +9587,10 @@
       <c r="A62" s="4"/>
       <c r="B62" s="93"/>
       <c r="D62" s="5"/>
-      <c r="E62" s="122"/>
-      <c r="F62" s="123"/>
-      <c r="G62" s="124"/>
-      <c r="H62" s="125"/>
+      <c r="E62" s="111"/>
+      <c r="F62" s="112"/>
+      <c r="G62" s="113"/>
+      <c r="H62" s="114"/>
       <c r="I62" s="10"/>
       <c r="J62" s="11"/>
       <c r="K62" s="4"/>
@@ -9642,10 +9654,10 @@
       <c r="A63" s="4"/>
       <c r="B63" s="93"/>
       <c r="D63" s="5"/>
-      <c r="E63" s="122"/>
-      <c r="F63" s="123"/>
-      <c r="G63" s="124"/>
-      <c r="H63" s="125"/>
+      <c r="E63" s="111"/>
+      <c r="F63" s="112"/>
+      <c r="G63" s="113"/>
+      <c r="H63" s="114"/>
       <c r="I63" s="10"/>
       <c r="J63" s="11"/>
       <c r="K63" s="4"/>
@@ -9709,10 +9721,10 @@
       <c r="A64" s="4"/>
       <c r="B64" s="93"/>
       <c r="D64" s="5"/>
-      <c r="E64" s="122"/>
-      <c r="F64" s="123"/>
-      <c r="G64" s="124"/>
-      <c r="H64" s="125"/>
+      <c r="E64" s="111"/>
+      <c r="F64" s="112"/>
+      <c r="G64" s="113"/>
+      <c r="H64" s="114"/>
       <c r="I64" s="10"/>
       <c r="J64" s="11"/>
       <c r="K64" s="4"/>
@@ -9776,10 +9788,10 @@
       <c r="A65" s="4"/>
       <c r="B65" s="93"/>
       <c r="D65" s="5"/>
-      <c r="E65" s="122"/>
-      <c r="F65" s="123"/>
-      <c r="G65" s="124"/>
-      <c r="H65" s="125"/>
+      <c r="E65" s="111"/>
+      <c r="F65" s="112"/>
+      <c r="G65" s="113"/>
+      <c r="H65" s="114"/>
       <c r="I65" s="10"/>
       <c r="J65" s="11"/>
       <c r="K65" s="4"/>
@@ -9843,10 +9855,10 @@
       <c r="A66" s="4"/>
       <c r="B66" s="93"/>
       <c r="D66" s="5"/>
-      <c r="E66" s="122"/>
-      <c r="F66" s="123"/>
-      <c r="G66" s="124"/>
-      <c r="H66" s="125"/>
+      <c r="E66" s="111"/>
+      <c r="F66" s="112"/>
+      <c r="G66" s="113"/>
+      <c r="H66" s="114"/>
       <c r="I66" s="10"/>
       <c r="J66" s="11"/>
       <c r="K66" s="4"/>
@@ -9910,10 +9922,10 @@
       <c r="A67" s="4"/>
       <c r="B67" s="93"/>
       <c r="D67" s="5"/>
-      <c r="E67" s="122"/>
-      <c r="F67" s="123"/>
-      <c r="G67" s="124"/>
-      <c r="H67" s="125"/>
+      <c r="E67" s="111"/>
+      <c r="F67" s="112"/>
+      <c r="G67" s="113"/>
+      <c r="H67" s="114"/>
       <c r="I67" s="10"/>
       <c r="J67" s="11"/>
       <c r="K67" s="4"/>
@@ -9977,10 +9989,10 @@
       <c r="A68" s="4"/>
       <c r="B68" s="93"/>
       <c r="D68" s="5"/>
-      <c r="E68" s="122"/>
-      <c r="F68" s="123"/>
-      <c r="G68" s="124"/>
-      <c r="H68" s="125"/>
+      <c r="E68" s="111"/>
+      <c r="F68" s="112"/>
+      <c r="G68" s="113"/>
+      <c r="H68" s="114"/>
       <c r="I68" s="10"/>
       <c r="J68" s="11"/>
       <c r="K68" s="4"/>
@@ -10044,10 +10056,10 @@
       <c r="A69" s="4"/>
       <c r="B69" s="93"/>
       <c r="D69" s="5"/>
-      <c r="E69" s="122"/>
-      <c r="F69" s="123"/>
-      <c r="G69" s="124"/>
-      <c r="H69" s="125"/>
+      <c r="E69" s="111"/>
+      <c r="F69" s="112"/>
+      <c r="G69" s="113"/>
+      <c r="H69" s="114"/>
       <c r="I69" s="10"/>
       <c r="J69" s="11"/>
       <c r="K69" s="4"/>
@@ -10111,10 +10123,10 @@
       <c r="A70" s="4"/>
       <c r="B70" s="93"/>
       <c r="D70" s="5"/>
-      <c r="E70" s="122"/>
-      <c r="F70" s="123"/>
-      <c r="G70" s="124"/>
-      <c r="H70" s="125"/>
+      <c r="E70" s="111"/>
+      <c r="F70" s="112"/>
+      <c r="G70" s="113"/>
+      <c r="H70" s="114"/>
       <c r="I70" s="10"/>
       <c r="J70" s="11"/>
       <c r="K70" s="4"/>
@@ -10178,10 +10190,10 @@
       <c r="A71" s="4"/>
       <c r="B71" s="93"/>
       <c r="D71" s="5"/>
-      <c r="E71" s="122"/>
-      <c r="F71" s="123"/>
-      <c r="G71" s="124"/>
-      <c r="H71" s="125"/>
+      <c r="E71" s="111"/>
+      <c r="F71" s="112"/>
+      <c r="G71" s="113"/>
+      <c r="H71" s="114"/>
       <c r="I71" s="10"/>
       <c r="J71" s="11"/>
       <c r="K71" s="4"/>
@@ -10245,10 +10257,10 @@
       <c r="A72" s="4"/>
       <c r="B72" s="93"/>
       <c r="D72" s="5"/>
-      <c r="E72" s="122"/>
-      <c r="F72" s="123"/>
-      <c r="G72" s="124"/>
-      <c r="H72" s="125"/>
+      <c r="E72" s="111"/>
+      <c r="F72" s="112"/>
+      <c r="G72" s="113"/>
+      <c r="H72" s="114"/>
       <c r="I72" s="10"/>
       <c r="J72" s="11"/>
       <c r="K72" s="4"/>
@@ -10312,10 +10324,10 @@
       <c r="A73" s="4"/>
       <c r="B73" s="93"/>
       <c r="D73" s="5"/>
-      <c r="E73" s="122"/>
-      <c r="F73" s="123"/>
-      <c r="G73" s="124"/>
-      <c r="H73" s="125"/>
+      <c r="E73" s="111"/>
+      <c r="F73" s="112"/>
+      <c r="G73" s="113"/>
+      <c r="H73" s="114"/>
       <c r="I73" s="10"/>
       <c r="J73" s="11"/>
       <c r="K73" s="4"/>
@@ -10379,10 +10391,10 @@
       <c r="A74" s="4"/>
       <c r="B74" s="93"/>
       <c r="D74" s="5"/>
-      <c r="E74" s="122"/>
-      <c r="F74" s="123"/>
-      <c r="G74" s="124"/>
-      <c r="H74" s="125"/>
+      <c r="E74" s="111"/>
+      <c r="F74" s="112"/>
+      <c r="G74" s="113"/>
+      <c r="H74" s="114"/>
       <c r="I74" s="10"/>
       <c r="J74" s="11"/>
       <c r="K74" s="4"/>
@@ -10446,10 +10458,10 @@
       <c r="A75" s="4"/>
       <c r="B75" s="93"/>
       <c r="D75" s="5"/>
-      <c r="E75" s="122"/>
-      <c r="F75" s="123"/>
-      <c r="G75" s="124"/>
-      <c r="H75" s="125"/>
+      <c r="E75" s="111"/>
+      <c r="F75" s="112"/>
+      <c r="G75" s="113"/>
+      <c r="H75" s="114"/>
       <c r="I75" s="10"/>
       <c r="J75" s="11"/>
       <c r="K75" s="4"/>
@@ -13948,6 +13960,16 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0"/>
   <mergeCells count="19">
+    <mergeCell ref="K1:AE1"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="R4:X4"/>
+    <mergeCell ref="Y4:AE4"/>
+    <mergeCell ref="AF4:AL4"/>
+    <mergeCell ref="AM4:AS4"/>
+    <mergeCell ref="AT4:AZ4"/>
+    <mergeCell ref="BA4:BG4"/>
+    <mergeCell ref="BH4:BN4"/>
     <mergeCell ref="AM5:AS5"/>
     <mergeCell ref="AT5:AZ5"/>
     <mergeCell ref="BA5:BG5"/>
@@ -13957,16 +13979,6 @@
     <mergeCell ref="R5:X5"/>
     <mergeCell ref="Y5:AE5"/>
     <mergeCell ref="AF5:AL5"/>
-    <mergeCell ref="AF4:AL4"/>
-    <mergeCell ref="AM4:AS4"/>
-    <mergeCell ref="AT4:AZ4"/>
-    <mergeCell ref="BA4:BG4"/>
-    <mergeCell ref="BH4:BN4"/>
-    <mergeCell ref="K1:AE1"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="K4:Q4"/>
-    <mergeCell ref="R4:X4"/>
-    <mergeCell ref="Y4:AE4"/>
   </mergeCells>
   <conditionalFormatting sqref="H11">
     <cfRule type="dataBar" priority="157">
@@ -15247,10 +15259,10 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="18">
-      <c r="A13" s="120" t="s">
+      <c r="A13" s="124" t="s">
         <v>154</v>
       </c>
-      <c r="B13" s="120"/>
+      <c r="B13" s="124"/>
     </row>
     <row r="15" spans="1:3" s="22" customFormat="1" ht="18">
       <c r="A15" s="30"/>
@@ -15311,10 +15323,10 @@
       <c r="B23" s="36"/>
     </row>
     <row r="24" spans="1:3" ht="18">
-      <c r="A24" s="120" t="s">
+      <c r="A24" s="124" t="s">
         <v>165</v>
       </c>
-      <c r="B24" s="120"/>
+      <c r="B24" s="124"/>
     </row>
     <row r="25" spans="1:3" ht="43.5">
       <c r="A25" s="33"/>
@@ -15387,10 +15399,10 @@
       <c r="B37" s="36"/>
     </row>
     <row r="38" spans="1:2" ht="18">
-      <c r="A38" s="120" t="s">
+      <c r="A38" s="124" t="s">
         <v>175</v>
       </c>
-      <c r="B38" s="120"/>
+      <c r="B38" s="124"/>
     </row>
     <row r="39" spans="1:2" ht="28.5">
       <c r="B39" s="31" t="s">
@@ -15421,10 +15433,10 @@
       </c>
     </row>
     <row r="49" spans="1:2" ht="18">
-      <c r="A49" s="120" t="s">
+      <c r="A49" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="B49" s="120"/>
+      <c r="B49" s="124"/>
     </row>
     <row r="50" spans="1:2" ht="28.5">
       <c r="B50" s="31" t="s">
@@ -15519,10 +15531,10 @@
       <c r="B64" s="42"/>
     </row>
     <row r="65" spans="1:2" ht="18">
-      <c r="A65" s="120" t="s">
+      <c r="A65" s="124" t="s">
         <v>201</v>
       </c>
-      <c r="B65" s="120"/>
+      <c r="B65" s="124"/>
     </row>
     <row r="66" spans="1:2" ht="42.75">
       <c r="B66" s="31" t="s">
@@ -15530,10 +15542,10 @@
       </c>
     </row>
     <row r="68" spans="1:2" ht="18">
-      <c r="A68" s="120" t="s">
+      <c r="A68" s="124" t="s">
         <v>203</v>
       </c>
-      <c r="B68" s="120"/>
+      <c r="B68" s="124"/>
     </row>
     <row r="69" spans="1:2" ht="15">
       <c r="A69" s="43" t="s">
@@ -15895,32 +15907,52 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="49.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="37.5" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="125" t="s">
         <v>233</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
